--- a/Data/Excel/NLFS_III/Sanjeet_classification.xlsx
+++ b/Data/Excel/NLFS_III/Sanjeet_classification.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10709"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandeepsharma/Desktop/Research/Data Analysis/Formal Informal wage/Formal_Informal_wage/Data/Excel/NLFS_III/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Formal_Informal_wage\Data\Excel\NLFS_III\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{B6837F17-5056-6940-961A-26BC02949FF0}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228E3919-CE71-4005-AD81-3E56183F5B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="27320" windowHeight="14360" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="education_III" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6319" uniqueCount="1623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6319" uniqueCount="1624">
   <si>
     <t>value</t>
   </si>
@@ -4898,13 +4898,16 @@
   </si>
   <si>
     <t>gdp_sector</t>
+  </si>
+  <si>
+    <t>gdp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -5249,13 +5252,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="22.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.1640625" customWidth="1"/>
+    <col min="2" max="2" width="22.81640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5269,7 +5272,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5283,7 +5286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5297,7 +5300,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5311,7 +5314,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -5325,7 +5328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -5339,7 +5342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -5353,7 +5356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -5367,7 +5370,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -5381,7 +5384,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -5395,7 +5398,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -5409,7 +5412,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -5423,7 +5426,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -5437,7 +5440,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -5451,7 +5454,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -5465,7 +5468,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -5479,7 +5482,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -5493,7 +5496,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -5507,7 +5510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -5534,15 +5537,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F131"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="22.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.5" customWidth="1"/>
+    <col min="2" max="2" width="22.36328125" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" customWidth="1"/>
+    <col min="5" max="5" width="18.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16">
+    <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5562,7 +5565,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="16">
+    <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5582,7 +5585,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="16">
+    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5602,7 +5605,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="16">
+    <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5622,7 +5625,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="16">
+    <row r="5" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5642,7 +5645,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="16">
+    <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5662,7 +5665,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16">
+    <row r="7" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5682,7 +5685,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16">
+    <row r="8" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5702,7 +5705,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="16">
+    <row r="9" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5722,7 +5725,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="16">
+    <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5742,7 +5745,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="16">
+    <row r="11" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5762,7 +5765,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="16">
+    <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5782,7 +5785,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="16">
+    <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5802,7 +5805,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="16">
+    <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5822,7 +5825,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="16">
+    <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5842,7 +5845,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="16">
+    <row r="16" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5862,7 +5865,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="16">
+    <row r="17" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5882,7 +5885,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="16">
+    <row r="18" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5902,7 +5905,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="16">
+    <row r="19" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5922,7 +5925,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="16">
+    <row r="20" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5942,7 +5945,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="16">
+    <row r="21" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5962,7 +5965,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="16">
+    <row r="22" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5982,7 +5985,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="16">
+    <row r="23" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -6002,7 +6005,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="16">
+    <row r="24" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -6022,7 +6025,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="16">
+    <row r="25" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -6042,7 +6045,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="16">
+    <row r="26" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -6062,7 +6065,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16">
+    <row r="27" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -6082,7 +6085,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="16">
+    <row r="28" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -6102,7 +6105,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="16">
+    <row r="29" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -6122,7 +6125,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="16">
+    <row r="30" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -6142,7 +6145,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="16">
+    <row r="31" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -6162,7 +6165,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="16">
+    <row r="32" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6182,7 +6185,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="16">
+    <row r="33" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6202,7 +6205,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="16">
+    <row r="34" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -6222,7 +6225,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="16">
+    <row r="35" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6242,7 +6245,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="16">
+    <row r="36" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6262,7 +6265,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="16">
+    <row r="37" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -6282,7 +6285,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="16">
+    <row r="38" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6302,7 +6305,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="16">
+    <row r="39" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6322,7 +6325,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="16">
+    <row r="40" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6342,7 +6345,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="16">
+    <row r="41" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -6362,7 +6365,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="16">
+    <row r="42" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -6382,7 +6385,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="16">
+    <row r="43" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6402,7 +6405,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="16">
+    <row r="44" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6422,7 +6425,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="16">
+    <row r="45" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6442,7 +6445,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="16">
+    <row r="46" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6462,7 +6465,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="16">
+    <row r="47" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6482,7 +6485,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="16">
+    <row r="48" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6502,7 +6505,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="16">
+    <row r="49" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6522,7 +6525,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="16">
+    <row r="50" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6542,7 +6545,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="16">
+    <row r="51" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6562,7 +6565,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="16">
+    <row r="52" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6582,7 +6585,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="16">
+    <row r="53" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6602,7 +6605,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="16">
+    <row r="54" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6622,7 +6625,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="16">
+    <row r="55" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6642,7 +6645,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="16">
+    <row r="56" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6662,7 +6665,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="16">
+    <row r="57" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6682,7 +6685,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="16">
+    <row r="58" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6702,7 +6705,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="16">
+    <row r="59" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6722,7 +6725,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="16">
+    <row r="60" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6742,7 +6745,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="16">
+    <row r="61" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6762,7 +6765,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="16">
+    <row r="62" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6782,7 +6785,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="16">
+    <row r="63" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6802,7 +6805,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="16">
+    <row r="64" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6822,7 +6825,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="16">
+    <row r="65" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6842,7 +6845,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="16">
+    <row r="66" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6862,7 +6865,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="16">
+    <row r="67" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6882,7 +6885,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="16">
+    <row r="68" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6902,7 +6905,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="16">
+    <row r="69" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6922,7 +6925,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="16">
+    <row r="70" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6942,7 +6945,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16">
+    <row r="71" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6962,7 +6965,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="16">
+    <row r="72" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6982,7 +6985,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="16">
+    <row r="73" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -7002,7 +7005,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="16">
+    <row r="74" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -7022,7 +7025,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="16">
+    <row r="75" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -7042,7 +7045,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="16">
+    <row r="76" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -7062,7 +7065,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="16">
+    <row r="77" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -7082,7 +7085,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="16">
+    <row r="78" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -7102,7 +7105,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="16">
+    <row r="79" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -7122,7 +7125,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="16">
+    <row r="80" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -7142,7 +7145,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="16">
+    <row r="81" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -7162,7 +7165,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="16">
+    <row r="82" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -7182,7 +7185,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="16">
+    <row r="83" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>83</v>
       </c>
@@ -7202,7 +7205,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="16">
+    <row r="84" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>84</v>
       </c>
@@ -7222,7 +7225,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="16">
+    <row r="85" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>85</v>
       </c>
@@ -7242,7 +7245,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="16">
+    <row r="86" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>86</v>
       </c>
@@ -7262,7 +7265,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="16">
+    <row r="87" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>87</v>
       </c>
@@ -7282,7 +7285,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="16">
+    <row r="88" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>88</v>
       </c>
@@ -7302,7 +7305,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="16">
+    <row r="89" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>89</v>
       </c>
@@ -7322,7 +7325,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="16">
+    <row r="90" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>90</v>
       </c>
@@ -7342,7 +7345,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="16">
+    <row r="91" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>91</v>
       </c>
@@ -7362,7 +7365,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="16">
+    <row r="92" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>92</v>
       </c>
@@ -7382,7 +7385,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="16">
+    <row r="93" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>93</v>
       </c>
@@ -7402,7 +7405,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16">
+    <row r="94" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>94</v>
       </c>
@@ -7422,7 +7425,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="16">
+    <row r="95" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>96</v>
       </c>
@@ -7442,7 +7445,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="16">
+    <row r="96" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>97</v>
       </c>
@@ -7462,7 +7465,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="16">
+    <row r="97" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>98</v>
       </c>
@@ -7482,7 +7485,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="16">
+    <row r="98" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>99</v>
       </c>
@@ -7502,7 +7505,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="16">
+    <row r="99" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>100</v>
       </c>
@@ -7522,7 +7525,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="16">
+    <row r="100" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>110</v>
       </c>
@@ -7542,7 +7545,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="16">
+    <row r="101" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>115</v>
       </c>
@@ -7562,7 +7565,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="16">
+    <row r="102" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>116</v>
       </c>
@@ -7582,7 +7585,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="16">
+    <row r="103" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>117</v>
       </c>
@@ -7602,7 +7605,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="16">
+    <row r="104" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>118</v>
       </c>
@@ -7622,7 +7625,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="16">
+    <row r="105" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>119</v>
       </c>
@@ -7642,7 +7645,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="16">
+    <row r="106" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>120</v>
       </c>
@@ -7662,7 +7665,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="16">
+    <row r="107" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>121</v>
       </c>
@@ -7682,7 +7685,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="16">
+    <row r="108" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>122</v>
       </c>
@@ -7702,7 +7705,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="16">
+    <row r="109" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>123</v>
       </c>
@@ -7722,7 +7725,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="16">
+    <row r="110" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>124</v>
       </c>
@@ -7742,7 +7745,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="16">
+    <row r="111" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>125</v>
       </c>
@@ -7762,7 +7765,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="16">
+    <row r="112" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>126</v>
       </c>
@@ -7782,7 +7785,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="16">
+    <row r="113" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>127</v>
       </c>
@@ -7802,7 +7805,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="16">
+    <row r="114" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>128</v>
       </c>
@@ -7822,7 +7825,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="16">
+    <row r="115" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>129</v>
       </c>
@@ -7842,7 +7845,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="16">
+    <row r="116" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>130</v>
       </c>
@@ -7862,7 +7865,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="16">
+    <row r="117" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>131</v>
       </c>
@@ -7882,7 +7885,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="16">
+    <row r="118" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>132</v>
       </c>
@@ -7902,7 +7905,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="16">
+    <row r="119" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>133</v>
       </c>
@@ -7922,7 +7925,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="16">
+    <row r="120" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>134</v>
       </c>
@@ -7942,7 +7945,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="16">
+    <row r="121" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>135</v>
       </c>
@@ -7962,7 +7965,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="16">
+    <row r="122" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>136</v>
       </c>
@@ -7982,7 +7985,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="16">
+    <row r="123" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>137</v>
       </c>
@@ -8002,7 +8005,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="16">
+    <row r="124" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>138</v>
       </c>
@@ -8022,7 +8025,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="16">
+    <row r="125" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>139</v>
       </c>
@@ -8042,7 +8045,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="16">
+    <row r="126" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>140</v>
       </c>
@@ -8062,7 +8065,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="16">
+    <row r="127" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>991</v>
       </c>
@@ -8082,7 +8085,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="16">
+    <row r="128" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>992</v>
       </c>
@@ -8102,7 +8105,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="16">
+    <row r="129" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>993</v>
       </c>
@@ -8122,7 +8125,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="16">
+    <row r="130" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>994</v>
       </c>
@@ -8142,7 +8145,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="131" spans="1:6" ht="16">
+    <row r="131" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>995</v>
       </c>
@@ -8175,18 +8178,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P437"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="4"/>
-    <col min="2" max="2" width="53.1640625" customWidth="1"/>
-    <col min="11" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="63.5" customWidth="1"/>
-    <col min="14" max="14" width="40.33203125" customWidth="1"/>
-    <col min="15" max="15" width="38.6640625" customWidth="1"/>
-    <col min="16" max="16" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" style="4"/>
+    <col min="2" max="2" width="53.1796875" customWidth="1"/>
+    <col min="11" max="11" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="63.453125" customWidth="1"/>
+    <col min="14" max="14" width="40.36328125" customWidth="1"/>
+    <col min="15" max="15" width="38.6328125" customWidth="1"/>
+    <col min="16" max="16" width="19.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -8236,7 +8239,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>110</v>
       </c>
@@ -8280,7 +8283,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>192</v>
       </c>
@@ -8309,7 +8312,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>195</v>
       </c>
@@ -8353,7 +8356,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>198</v>
       </c>
@@ -8382,7 +8385,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>205</v>
       </c>
@@ -8426,7 +8429,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>207</v>
       </c>
@@ -8470,7 +8473,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>209</v>
       </c>
@@ -8514,7 +8517,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>211</v>
       </c>
@@ -8543,7 +8546,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>213</v>
       </c>
@@ -8581,7 +8584,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>217</v>
       </c>
@@ -8625,7 +8628,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>219</v>
       </c>
@@ -8654,7 +8657,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>221</v>
       </c>
@@ -8683,7 +8686,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>223</v>
       </c>
@@ -8712,7 +8715,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>225</v>
       </c>
@@ -8741,7 +8744,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>227</v>
       </c>
@@ -8764,7 +8767,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>229</v>
       </c>
@@ -8787,7 +8790,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>233</v>
       </c>
@@ -8810,7 +8813,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>235</v>
       </c>
@@ -8839,7 +8842,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>237</v>
       </c>
@@ -8862,7 +8865,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>239</v>
       </c>
@@ -8891,7 +8894,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>241</v>
       </c>
@@ -8914,7 +8917,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>243</v>
       </c>
@@ -8937,7 +8940,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>245</v>
       </c>
@@ -8960,7 +8963,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>247</v>
       </c>
@@ -8989,7 +8992,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>249</v>
       </c>
@@ -9012,7 +9015,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>251</v>
       </c>
@@ -9035,7 +9038,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>253</v>
       </c>
@@ -9064,7 +9067,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>255</v>
       </c>
@@ -9108,7 +9111,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>257</v>
       </c>
@@ -9131,7 +9134,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>259</v>
       </c>
@@ -9160,7 +9163,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>263</v>
       </c>
@@ -9189,7 +9192,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>265</v>
       </c>
@@ -9218,7 +9221,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>267</v>
       </c>
@@ -9241,7 +9244,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>269</v>
       </c>
@@ -9270,7 +9273,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>271</v>
       </c>
@@ -9293,7 +9296,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>276</v>
       </c>
@@ -9316,7 +9319,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>278</v>
       </c>
@@ -9339,7 +9342,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>280</v>
       </c>
@@ -9362,7 +9365,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>282</v>
       </c>
@@ -9391,7 +9394,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>285</v>
       </c>
@@ -9414,7 +9417,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>287</v>
       </c>
@@ -9458,7 +9461,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>289</v>
       </c>
@@ -9487,7 +9490,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>291</v>
       </c>
@@ -9510,7 +9513,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>293</v>
       </c>
@@ -9539,7 +9542,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>295</v>
       </c>
@@ -9562,7 +9565,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>297</v>
       </c>
@@ -9591,7 +9594,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>299</v>
       </c>
@@ -9614,7 +9617,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>301</v>
       </c>
@@ -9637,7 +9640,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>303</v>
       </c>
@@ -9660,7 +9663,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>305</v>
       </c>
@@ -9689,7 +9692,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>307</v>
       </c>
@@ -9712,7 +9715,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>309</v>
       </c>
@@ -9744,7 +9747,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="54" spans="1:16">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>311</v>
       </c>
@@ -9767,7 +9770,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>313</v>
       </c>
@@ -9790,7 +9793,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>315</v>
       </c>
@@ -9819,7 +9822,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>317</v>
       </c>
@@ -9842,7 +9845,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>319</v>
       </c>
@@ -9865,7 +9868,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>321</v>
       </c>
@@ -9894,7 +9897,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>323</v>
       </c>
@@ -9938,7 +9941,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>327</v>
       </c>
@@ -9982,7 +9985,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>329</v>
       </c>
@@ -10014,7 +10017,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="63" spans="1:16">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>331</v>
       </c>
@@ -10040,7 +10043,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>333</v>
       </c>
@@ -10075,7 +10078,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="65" spans="1:16">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>335</v>
       </c>
@@ -10119,7 +10122,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>337</v>
       </c>
@@ -10148,7 +10151,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>339</v>
       </c>
@@ -10183,7 +10186,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>341</v>
       </c>
@@ -10212,7 +10215,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>343</v>
       </c>
@@ -10235,7 +10238,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="70" spans="1:16">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>345</v>
       </c>
@@ -10258,7 +10261,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="71" spans="1:16">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>347</v>
       </c>
@@ -10287,7 +10290,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="72" spans="1:16">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>349</v>
       </c>
@@ -10310,7 +10313,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>351</v>
       </c>
@@ -10333,7 +10336,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="74" spans="1:16">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>353</v>
       </c>
@@ -10362,7 +10365,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>355</v>
       </c>
@@ -10406,7 +10409,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>359</v>
       </c>
@@ -10444,7 +10447,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>361</v>
       </c>
@@ -10488,7 +10491,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>363</v>
       </c>
@@ -10526,7 +10529,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>365</v>
       </c>
@@ -10570,7 +10573,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="80" spans="1:16">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>367</v>
       </c>
@@ -10602,7 +10605,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>369</v>
       </c>
@@ -10640,7 +10643,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>371</v>
       </c>
@@ -10672,7 +10675,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>373</v>
       </c>
@@ -10698,7 +10701,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="84" spans="1:16">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>375</v>
       </c>
@@ -10733,7 +10736,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="85" spans="1:16">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>377</v>
       </c>
@@ -10780,7 +10783,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="86" spans="1:16">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>379</v>
       </c>
@@ -10818,7 +10821,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>381</v>
       </c>
@@ -10862,7 +10865,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="88" spans="1:16">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>385</v>
       </c>
@@ -10891,7 +10894,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="89" spans="1:16">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>387</v>
       </c>
@@ -10914,7 +10917,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="90" spans="1:16">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>389</v>
       </c>
@@ -10958,7 +10961,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="91" spans="1:16">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>391</v>
       </c>
@@ -10987,7 +10990,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>393</v>
       </c>
@@ -11016,7 +11019,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="93" spans="1:16">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>395</v>
       </c>
@@ -11060,7 +11063,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="94" spans="1:16">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>397</v>
       </c>
@@ -11089,7 +11092,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="95" spans="1:16">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>399</v>
       </c>
@@ -11127,7 +11130,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="96" spans="1:16">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>401</v>
       </c>
@@ -11156,7 +11159,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="97" spans="1:16">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>403</v>
       </c>
@@ -11185,7 +11188,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="98" spans="1:16">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>405</v>
       </c>
@@ -11208,7 +11211,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="99" spans="1:16">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>409</v>
       </c>
@@ -11231,7 +11234,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="100" spans="1:16">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>411</v>
       </c>
@@ -11254,7 +11257,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="101" spans="1:16">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>413</v>
       </c>
@@ -11283,7 +11286,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="102" spans="1:16">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
         <v>415</v>
       </c>
@@ -11306,7 +11309,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:16">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>417</v>
       </c>
@@ -11329,7 +11332,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="104" spans="1:16">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
         <v>419</v>
       </c>
@@ -11352,7 +11355,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="105" spans="1:16">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>421</v>
       </c>
@@ -11381,7 +11384,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="106" spans="1:16">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
         <v>423</v>
       </c>
@@ -11404,7 +11407,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="107" spans="1:16">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>425</v>
       </c>
@@ -11448,7 +11451,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="108" spans="1:16">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
         <v>429</v>
       </c>
@@ -11471,7 +11474,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="109" spans="1:16">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
         <v>431</v>
       </c>
@@ -11494,7 +11497,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="110" spans="1:16">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
         <v>433</v>
       </c>
@@ -11517,7 +11520,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="111" spans="1:16">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>435</v>
       </c>
@@ -11540,7 +11543,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="112" spans="1:16">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
         <v>437</v>
       </c>
@@ -11563,7 +11566,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="113" spans="1:16">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
         <v>439</v>
       </c>
@@ -11586,7 +11589,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
         <v>441</v>
       </c>
@@ -11609,7 +11612,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="115" spans="1:16">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
         <v>443</v>
       </c>
@@ -11632,7 +11635,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="116" spans="1:16">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
         <v>445</v>
       </c>
@@ -11661,7 +11664,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>447</v>
       </c>
@@ -11690,7 +11693,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
         <v>449</v>
       </c>
@@ -11713,7 +11716,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>451</v>
       </c>
@@ -11742,7 +11745,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:16">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
         <v>453</v>
       </c>
@@ -11765,7 +11768,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
         <v>455</v>
       </c>
@@ -11788,7 +11791,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="122" spans="1:16">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
         <v>457</v>
       </c>
@@ -11817,7 +11820,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
         <v>459</v>
       </c>
@@ -11846,7 +11849,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
         <v>461</v>
       </c>
@@ -11869,7 +11872,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
         <v>463</v>
       </c>
@@ -11892,7 +11895,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
         <v>465</v>
       </c>
@@ -11927,7 +11930,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
         <v>467</v>
       </c>
@@ -11956,7 +11959,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="128" spans="1:16">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
         <v>469</v>
       </c>
@@ -11985,7 +11988,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="129" spans="1:16">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
         <v>475</v>
       </c>
@@ -12029,7 +12032,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="130" spans="1:16">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
         <v>477</v>
       </c>
@@ -12058,7 +12061,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="131" spans="1:16">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
         <v>479</v>
       </c>
@@ -12081,7 +12084,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="132" spans="1:16">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
         <v>481</v>
       </c>
@@ -12113,7 +12116,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="133" spans="1:16">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
         <v>483</v>
       </c>
@@ -12142,7 +12145,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="134" spans="1:16">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
         <v>485</v>
       </c>
@@ -12165,7 +12168,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="135" spans="1:16">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
         <v>487</v>
       </c>
@@ -12194,7 +12197,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="136" spans="1:16">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
         <v>489</v>
       </c>
@@ -12223,7 +12226,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="137" spans="1:16">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
         <v>491</v>
       </c>
@@ -12246,7 +12249,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="138" spans="1:16">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
         <v>493</v>
       </c>
@@ -12275,7 +12278,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="139" spans="1:16">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
         <v>495</v>
       </c>
@@ -12304,7 +12307,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="140" spans="1:16">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
         <v>497</v>
       </c>
@@ -12333,7 +12336,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="141" spans="1:16">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
         <v>499</v>
       </c>
@@ -12356,7 +12359,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="142" spans="1:16">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
         <v>501</v>
       </c>
@@ -12379,7 +12382,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="143" spans="1:16">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
         <v>503</v>
       </c>
@@ -12408,7 +12411,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="144" spans="1:16">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
         <v>505</v>
       </c>
@@ -12431,7 +12434,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="145" spans="1:16">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
         <v>507</v>
       </c>
@@ -12454,7 +12457,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="146" spans="1:16">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
         <v>509</v>
       </c>
@@ -12486,7 +12489,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="147" spans="1:16">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>511</v>
       </c>
@@ -12524,7 +12527,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="148" spans="1:16">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>513</v>
       </c>
@@ -12568,7 +12571,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="149" spans="1:16">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
         <v>515</v>
       </c>
@@ -12591,7 +12594,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="150" spans="1:16">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
         <v>517</v>
       </c>
@@ -12614,7 +12617,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="151" spans="1:16">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
         <v>519</v>
       </c>
@@ -12643,7 +12646,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="152" spans="1:16">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
         <v>521</v>
       </c>
@@ -12672,7 +12675,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="153" spans="1:16">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
         <v>523</v>
       </c>
@@ -12695,7 +12698,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="154" spans="1:16">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
         <v>525</v>
       </c>
@@ -12733,7 +12736,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="155" spans="1:16">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
         <v>529</v>
       </c>
@@ -12777,7 +12780,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="156" spans="1:16">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
         <v>531</v>
       </c>
@@ -12821,7 +12824,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="157" spans="1:16">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
         <v>533</v>
       </c>
@@ -12850,7 +12853,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="158" spans="1:16">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
         <v>535</v>
       </c>
@@ -12894,7 +12897,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="159" spans="1:16">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
         <v>537</v>
       </c>
@@ -12926,7 +12929,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="160" spans="1:16">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
         <v>539</v>
       </c>
@@ -12949,7 +12952,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="161" spans="1:16">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
         <v>541</v>
       </c>
@@ -12993,7 +12996,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="162" spans="1:16">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>543</v>
       </c>
@@ -13016,7 +13019,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="163" spans="1:16">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>545</v>
       </c>
@@ -13045,7 +13048,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="164" spans="1:16">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
         <v>547</v>
       </c>
@@ -13083,7 +13086,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="165" spans="1:16">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>549</v>
       </c>
@@ -13106,7 +13109,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="166" spans="1:16">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
         <v>551</v>
       </c>
@@ -13129,7 +13132,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="167" spans="1:16">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
         <v>553</v>
       </c>
@@ -13167,7 +13170,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="168" spans="1:16">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
         <v>555</v>
       </c>
@@ -13196,7 +13199,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="169" spans="1:16">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
         <v>557</v>
       </c>
@@ -13219,7 +13222,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="170" spans="1:16">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
         <v>559</v>
       </c>
@@ -13248,7 +13251,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="171" spans="1:16">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
         <v>561</v>
       </c>
@@ -13277,7 +13280,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="172" spans="1:16">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
         <v>565</v>
       </c>
@@ -13321,7 +13324,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="173" spans="1:16">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
         <v>567</v>
       </c>
@@ -13365,7 +13368,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="174" spans="1:16">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
         <v>569</v>
       </c>
@@ -13394,7 +13397,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="175" spans="1:16">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
         <v>571</v>
       </c>
@@ -13423,7 +13426,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="176" spans="1:16">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
         <v>573</v>
       </c>
@@ -13452,7 +13455,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="177" spans="1:16">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
         <v>575</v>
       </c>
@@ -13496,7 +13499,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="178" spans="1:16">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
         <v>577</v>
       </c>
@@ -13519,7 +13522,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="179" spans="1:16">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
         <v>579</v>
       </c>
@@ -13548,7 +13551,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="180" spans="1:16">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
         <v>581</v>
       </c>
@@ -13577,7 +13580,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="181" spans="1:16">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
         <v>583</v>
       </c>
@@ -13606,7 +13609,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="182" spans="1:16">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
         <v>585</v>
       </c>
@@ -13641,7 +13644,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="183" spans="1:16">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
         <v>587</v>
       </c>
@@ -13670,7 +13673,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="184" spans="1:16">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
         <v>589</v>
       </c>
@@ -13699,7 +13702,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="185" spans="1:16">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
         <v>591</v>
       </c>
@@ -13743,7 +13746,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="186" spans="1:16">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
         <v>593</v>
       </c>
@@ -13766,7 +13769,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="187" spans="1:16">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
         <v>595</v>
       </c>
@@ -13810,7 +13813,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="188" spans="1:16">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
         <v>597</v>
       </c>
@@ -13839,7 +13842,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="189" spans="1:16">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
         <v>599</v>
       </c>
@@ -13862,7 +13865,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="190" spans="1:16">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
         <v>601</v>
       </c>
@@ -13891,7 +13894,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="191" spans="1:16">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
         <v>603</v>
       </c>
@@ -13935,7 +13938,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="192" spans="1:16">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
         <v>605</v>
       </c>
@@ -13964,7 +13967,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="193" spans="1:16">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
         <v>607</v>
       </c>
@@ -14008,7 +14011,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="194" spans="1:16">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
         <v>609</v>
       </c>
@@ -14037,7 +14040,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="195" spans="1:16">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
         <v>611</v>
       </c>
@@ -14069,7 +14072,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="196" spans="1:16">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
         <v>615</v>
       </c>
@@ -14107,7 +14110,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="197" spans="1:16">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
         <v>617</v>
       </c>
@@ -14136,7 +14139,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="198" spans="1:16">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A198" s="4" t="s">
         <v>619</v>
       </c>
@@ -14165,7 +14168,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="199" spans="1:16">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A199" s="4" t="s">
         <v>621</v>
       </c>
@@ -14194,7 +14197,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="200" spans="1:16">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A200" s="4" t="s">
         <v>623</v>
       </c>
@@ -14217,7 +14220,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="201" spans="1:16">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
         <v>625</v>
       </c>
@@ -14240,7 +14243,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="202" spans="1:16">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
         <v>627</v>
       </c>
@@ -14263,7 +14266,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="203" spans="1:16">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
         <v>629</v>
       </c>
@@ -14286,7 +14289,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="204" spans="1:16">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
         <v>631</v>
       </c>
@@ -14315,7 +14318,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="205" spans="1:16">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
         <v>633</v>
       </c>
@@ -14344,7 +14347,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="1:16">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A206" s="4" t="s">
         <v>635</v>
       </c>
@@ -14382,7 +14385,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="207" spans="1:16">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
         <v>639</v>
       </c>
@@ -14417,7 +14420,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="208" spans="1:16">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="s">
         <v>641</v>
       </c>
@@ -14446,7 +14449,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="209" spans="1:16">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
         <v>643</v>
       </c>
@@ -14469,7 +14472,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="210" spans="1:16">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="s">
         <v>645</v>
       </c>
@@ -14513,7 +14516,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="211" spans="1:16">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
         <v>647</v>
       </c>
@@ -14557,7 +14560,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="212" spans="1:16">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="s">
         <v>649</v>
       </c>
@@ -14601,7 +14604,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="213" spans="1:16">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
         <v>656</v>
       </c>
@@ -14645,7 +14648,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="214" spans="1:16">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
         <v>658</v>
       </c>
@@ -14683,7 +14686,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="215" spans="1:16">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
         <v>660</v>
       </c>
@@ -14727,7 +14730,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="216" spans="1:16">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="s">
         <v>662</v>
       </c>
@@ -14765,7 +14768,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="217" spans="1:16">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
         <v>666</v>
       </c>
@@ -14794,7 +14797,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="218" spans="1:16">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
         <v>668</v>
       </c>
@@ -14817,7 +14820,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="219" spans="1:16">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A219" s="4" t="s">
         <v>670</v>
       </c>
@@ -14858,7 +14861,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="220" spans="1:16">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A220" s="4" t="s">
         <v>672</v>
       </c>
@@ -14887,7 +14890,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="221" spans="1:16">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A221" s="4" t="s">
         <v>674</v>
       </c>
@@ -14916,7 +14919,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="222" spans="1:16">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A222" s="4" t="s">
         <v>676</v>
       </c>
@@ -14945,7 +14948,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="223" spans="1:16">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A223" s="4" t="s">
         <v>678</v>
       </c>
@@ -14977,7 +14980,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="224" spans="1:16">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A224" s="4" t="s">
         <v>680</v>
       </c>
@@ -15012,7 +15015,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="225" spans="1:16">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="s">
         <v>682</v>
       </c>
@@ -15053,7 +15056,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="226" spans="1:16">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="s">
         <v>684</v>
       </c>
@@ -15091,7 +15094,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="227" spans="1:16">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="s">
         <v>686</v>
       </c>
@@ -15129,7 +15132,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="228" spans="1:16">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A228" s="4" t="s">
         <v>688</v>
       </c>
@@ -15167,7 +15170,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="229" spans="1:16">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="s">
         <v>692</v>
       </c>
@@ -15211,7 +15214,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="230" spans="1:16">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A230" s="4" t="s">
         <v>694</v>
       </c>
@@ -15240,7 +15243,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="231" spans="1:16">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="s">
         <v>696</v>
       </c>
@@ -15269,7 +15272,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="232" spans="1:16">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="s">
         <v>698</v>
       </c>
@@ -15301,7 +15304,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="233" spans="1:16">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
         <v>700</v>
       </c>
@@ -15324,7 +15327,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="234" spans="1:16">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="s">
         <v>702</v>
       </c>
@@ -15353,7 +15356,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="235" spans="1:16">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
         <v>706</v>
       </c>
@@ -15397,7 +15400,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="236" spans="1:16">
+    <row r="236" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A236" s="4" t="s">
         <v>708</v>
       </c>
@@ -15426,7 +15429,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="237" spans="1:16">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="s">
         <v>710</v>
       </c>
@@ -15470,7 +15473,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="238" spans="1:16">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A238" s="4" t="s">
         <v>712</v>
       </c>
@@ -15505,7 +15508,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="239" spans="1:16">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
         <v>714</v>
       </c>
@@ -15549,7 +15552,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="240" spans="1:16">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A240" s="4" t="s">
         <v>716</v>
       </c>
@@ -15593,7 +15596,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="241" spans="1:16">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A241" s="4" t="s">
         <v>718</v>
       </c>
@@ -15637,7 +15640,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="242" spans="1:16">
+    <row r="242" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A242" s="4" t="s">
         <v>724</v>
       </c>
@@ -15666,7 +15669,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="243" spans="1:16">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A243" s="4" t="s">
         <v>726</v>
       </c>
@@ -15695,7 +15698,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="244" spans="1:16">
+    <row r="244" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A244" s="4" t="s">
         <v>728</v>
       </c>
@@ -15739,7 +15742,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="245" spans="1:16">
+    <row r="245" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
         <v>730</v>
       </c>
@@ -15783,7 +15786,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="246" spans="1:16">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A246" s="4" t="s">
         <v>732</v>
       </c>
@@ -15812,7 +15815,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="247" spans="1:16">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A247" s="4" t="s">
         <v>734</v>
       </c>
@@ -15856,7 +15859,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="248" spans="1:16">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A248" s="4" t="s">
         <v>736</v>
       </c>
@@ -15885,7 +15888,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="249" spans="1:16">
+    <row r="249" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A249" s="4" t="s">
         <v>738</v>
       </c>
@@ -15923,7 +15926,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="250" spans="1:16">
+    <row r="250" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A250" s="4" t="s">
         <v>740</v>
       </c>
@@ -15955,7 +15958,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="251" spans="1:16">
+    <row r="251" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
         <v>742</v>
       </c>
@@ -15999,7 +16002,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="252" spans="1:16">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A252" s="4" t="s">
         <v>744</v>
       </c>
@@ -16028,7 +16031,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="253" spans="1:16">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
         <v>746</v>
       </c>
@@ -16051,7 +16054,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="254" spans="1:16">
+    <row r="254" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A254" s="4" t="s">
         <v>748</v>
       </c>
@@ -16080,7 +16083,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="255" spans="1:16">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A255" s="4" t="s">
         <v>750</v>
       </c>
@@ -16103,7 +16106,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="256" spans="1:16">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A256" s="4" t="s">
         <v>752</v>
       </c>
@@ -16132,7 +16135,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="257" spans="1:16">
+    <row r="257" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A257" s="4" t="s">
         <v>754</v>
       </c>
@@ -16167,7 +16170,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="258" spans="1:16">
+    <row r="258" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A258" s="4" t="s">
         <v>756</v>
       </c>
@@ -16205,7 +16208,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="259" spans="1:16">
+    <row r="259" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
         <v>760</v>
       </c>
@@ -16243,7 +16246,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="260" spans="1:16">
+    <row r="260" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A260" s="4" t="s">
         <v>762</v>
       </c>
@@ -16287,7 +16290,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="261" spans="1:16">
+    <row r="261" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A261" s="4" t="s">
         <v>764</v>
       </c>
@@ -16331,7 +16334,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="262" spans="1:16">
+    <row r="262" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A262" s="4" t="s">
         <v>766</v>
       </c>
@@ -16375,7 +16378,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="263" spans="1:16">
+    <row r="263" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
         <v>768</v>
       </c>
@@ -16419,7 +16422,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="264" spans="1:16">
+    <row r="264" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A264" s="4" t="s">
         <v>770</v>
       </c>
@@ -16442,7 +16445,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="265" spans="1:16">
+    <row r="265" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
         <v>772</v>
       </c>
@@ -16486,7 +16489,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="266" spans="1:16">
+    <row r="266" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A266" s="4" t="s">
         <v>774</v>
       </c>
@@ -16530,7 +16533,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="267" spans="1:16">
+    <row r="267" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A267" s="4" t="s">
         <v>776</v>
       </c>
@@ -16559,7 +16562,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="268" spans="1:16">
+    <row r="268" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A268" s="4" t="s">
         <v>778</v>
       </c>
@@ -16597,7 +16600,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="269" spans="1:16">
+    <row r="269" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A269" s="4" t="s">
         <v>780</v>
       </c>
@@ -16629,7 +16632,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="270" spans="1:16">
+    <row r="270" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A270" s="4" t="s">
         <v>782</v>
       </c>
@@ -16658,7 +16661,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="271" spans="1:16">
+    <row r="271" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A271" s="4" t="s">
         <v>784</v>
       </c>
@@ -16687,7 +16690,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="272" spans="1:16">
+    <row r="272" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A272" s="4" t="s">
         <v>788</v>
       </c>
@@ -16722,7 +16725,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="273" spans="1:16">
+    <row r="273" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A273" s="4" t="s">
         <v>790</v>
       </c>
@@ -16763,7 +16766,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="274" spans="1:16">
+    <row r="274" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A274" s="4" t="s">
         <v>792</v>
       </c>
@@ -16792,7 +16795,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="275" spans="1:16">
+    <row r="275" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A275" s="4" t="s">
         <v>794</v>
       </c>
@@ -16821,7 +16824,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="276" spans="1:16">
+    <row r="276" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A276" s="4" t="s">
         <v>796</v>
       </c>
@@ -16844,7 +16847,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="277" spans="1:16">
+    <row r="277" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
         <v>800</v>
       </c>
@@ -16888,7 +16891,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="278" spans="1:16">
+    <row r="278" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
         <v>802</v>
       </c>
@@ -16911,7 +16914,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="279" spans="1:16">
+    <row r="279" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
         <v>804</v>
       </c>
@@ -16955,7 +16958,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="280" spans="1:16">
+    <row r="280" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
         <v>806</v>
       </c>
@@ -16999,7 +17002,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="281" spans="1:16">
+    <row r="281" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
         <v>808</v>
       </c>
@@ -17034,7 +17037,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="282" spans="1:16">
+    <row r="282" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
         <v>814</v>
       </c>
@@ -17072,7 +17075,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="283" spans="1:16">
+    <row r="283" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
         <v>816</v>
       </c>
@@ -17116,7 +17119,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="284" spans="1:16">
+    <row r="284" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
         <v>818</v>
       </c>
@@ -17154,7 +17157,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="285" spans="1:16">
+    <row r="285" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
         <v>820</v>
       </c>
@@ -17183,7 +17186,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="286" spans="1:16">
+    <row r="286" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A286" s="4" t="s">
         <v>822</v>
       </c>
@@ -17221,7 +17224,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="287" spans="1:16">
+    <row r="287" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
         <v>824</v>
       </c>
@@ -17244,7 +17247,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="288" spans="1:16">
+    <row r="288" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A288" s="4" t="s">
         <v>826</v>
       </c>
@@ -17267,7 +17270,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="289" spans="1:16">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
         <v>828</v>
       </c>
@@ -17302,7 +17305,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="290" spans="1:16">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A290" s="4" t="s">
         <v>830</v>
       </c>
@@ -17334,7 +17337,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="291" spans="1:16">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A291" s="4" t="s">
         <v>834</v>
       </c>
@@ -17357,7 +17360,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="292" spans="1:16">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A292" s="4" t="s">
         <v>836</v>
       </c>
@@ -17380,7 +17383,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="293" spans="1:16">
+    <row r="293" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A293" s="4" t="s">
         <v>838</v>
       </c>
@@ -17403,7 +17406,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="294" spans="1:16">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A294" s="4" t="s">
         <v>840</v>
       </c>
@@ -17426,7 +17429,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="295" spans="1:16">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A295" s="4" t="s">
         <v>842</v>
       </c>
@@ -17461,7 +17464,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="296" spans="1:16">
+    <row r="296" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A296" s="4" t="s">
         <v>846</v>
       </c>
@@ -17484,7 +17487,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="297" spans="1:16">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A297" s="4" t="s">
         <v>848</v>
       </c>
@@ -17525,7 +17528,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="298" spans="1:16">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A298" s="4" t="s">
         <v>850</v>
       </c>
@@ -17554,7 +17557,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="299" spans="1:16">
+    <row r="299" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A299" s="4" t="s">
         <v>852</v>
       </c>
@@ -17598,7 +17601,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="300" spans="1:16">
+    <row r="300" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A300" s="4" t="s">
         <v>858</v>
       </c>
@@ -17642,7 +17645,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="301" spans="1:16">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A301" s="4" t="s">
         <v>860</v>
       </c>
@@ -17686,7 +17689,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="302" spans="1:16">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A302" s="4" t="s">
         <v>862</v>
       </c>
@@ -17730,7 +17733,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="303" spans="1:16">
+    <row r="303" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A303" s="4" t="s">
         <v>864</v>
       </c>
@@ -17774,7 +17777,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="304" spans="1:16">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A304" s="4" t="s">
         <v>866</v>
       </c>
@@ -17803,7 +17806,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="305" spans="1:16">
+    <row r="305" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A305" s="4" t="s">
         <v>868</v>
       </c>
@@ -17847,7 +17850,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="306" spans="1:16">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A306" s="4" t="s">
         <v>870</v>
       </c>
@@ -17876,7 +17879,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="307" spans="1:16">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A307" s="4" t="s">
         <v>872</v>
       </c>
@@ -17905,7 +17908,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="308" spans="1:16">
+    <row r="308" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A308" s="4" t="s">
         <v>874</v>
       </c>
@@ -17928,7 +17931,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="309" spans="1:16">
+    <row r="309" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A309" s="4" t="s">
         <v>876</v>
       </c>
@@ -17957,7 +17960,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="310" spans="1:16">
+    <row r="310" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A310" s="4" t="s">
         <v>878</v>
       </c>
@@ -17986,7 +17989,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="311" spans="1:16">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A311" s="4" t="s">
         <v>880</v>
       </c>
@@ -18009,7 +18012,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="312" spans="1:16">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A312" s="4" t="s">
         <v>882</v>
       </c>
@@ -18053,7 +18056,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="313" spans="1:16">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A313" s="4" t="s">
         <v>884</v>
       </c>
@@ -18097,7 +18100,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="314" spans="1:16">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A314" s="4" t="s">
         <v>886</v>
       </c>
@@ -18120,7 +18123,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="315" spans="1:16">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A315" s="4" t="s">
         <v>888</v>
       </c>
@@ -18149,7 +18152,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="316" spans="1:16">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A316" s="4" t="s">
         <v>892</v>
       </c>
@@ -18178,7 +18181,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="317" spans="1:16">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A317" s="4" t="s">
         <v>894</v>
       </c>
@@ -18207,7 +18210,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="318" spans="1:16">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A318" s="4" t="s">
         <v>896</v>
       </c>
@@ -18236,7 +18239,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="319" spans="1:16">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A319" s="4" t="s">
         <v>898</v>
       </c>
@@ -18265,7 +18268,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="320" spans="1:16">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A320" s="4" t="s">
         <v>900</v>
       </c>
@@ -18294,7 +18297,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="321" spans="1:16">
+    <row r="321" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A321" s="4" t="s">
         <v>902</v>
       </c>
@@ -18323,7 +18326,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="322" spans="1:16">
+    <row r="322" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A322" s="4" t="s">
         <v>904</v>
       </c>
@@ -18352,7 +18355,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="323" spans="1:16">
+    <row r="323" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A323" s="4" t="s">
         <v>906</v>
       </c>
@@ -18381,7 +18384,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="324" spans="1:16">
+    <row r="324" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A324" s="4" t="s">
         <v>908</v>
       </c>
@@ -18410,7 +18413,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="325" spans="1:16">
+    <row r="325" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A325" s="4" t="s">
         <v>910</v>
       </c>
@@ -18433,7 +18436,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="326" spans="1:16">
+    <row r="326" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A326" s="4" t="s">
         <v>912</v>
       </c>
@@ -18462,7 +18465,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="327" spans="1:16">
+    <row r="327" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A327" s="4" t="s">
         <v>914</v>
       </c>
@@ -18491,7 +18494,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="328" spans="1:16">
+    <row r="328" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A328" s="4" t="s">
         <v>916</v>
       </c>
@@ -18520,7 +18523,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="329" spans="1:16">
+    <row r="329" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A329" s="4" t="s">
         <v>920</v>
       </c>
@@ -18549,7 +18552,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="330" spans="1:16">
+    <row r="330" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A330" s="4" t="s">
         <v>922</v>
       </c>
@@ -18578,7 +18581,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="331" spans="1:16">
+    <row r="331" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A331" s="4" t="s">
         <v>924</v>
       </c>
@@ -18607,7 +18610,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="332" spans="1:16">
+    <row r="332" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A332" s="4" t="s">
         <v>926</v>
       </c>
@@ -18636,7 +18639,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="333" spans="1:16">
+    <row r="333" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A333" s="4" t="s">
         <v>928</v>
       </c>
@@ -18665,7 +18668,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="334" spans="1:16">
+    <row r="334" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A334" s="4" t="s">
         <v>930</v>
       </c>
@@ -18694,7 +18697,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="335" spans="1:16">
+    <row r="335" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A335" s="4" t="s">
         <v>932</v>
       </c>
@@ -18735,7 +18738,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="336" spans="1:16">
+    <row r="336" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A336" s="4" t="s">
         <v>934</v>
       </c>
@@ -18767,7 +18770,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="337" spans="1:16">
+    <row r="337" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A337" s="4" t="s">
         <v>936</v>
       </c>
@@ -18796,7 +18799,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="338" spans="1:16">
+    <row r="338" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A338" s="4" t="s">
         <v>938</v>
       </c>
@@ -18825,7 +18828,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="339" spans="1:16">
+    <row r="339" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A339" s="4" t="s">
         <v>940</v>
       </c>
@@ -18854,7 +18857,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="340" spans="1:16">
+    <row r="340" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A340" s="4" t="s">
         <v>942</v>
       </c>
@@ -18883,7 +18886,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="341" spans="1:16">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A341" s="4" t="s">
         <v>946</v>
       </c>
@@ -18912,7 +18915,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="342" spans="1:16">
+    <row r="342" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A342" s="4" t="s">
         <v>948</v>
       </c>
@@ -18941,7 +18944,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="343" spans="1:16">
+    <row r="343" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A343" s="4" t="s">
         <v>950</v>
       </c>
@@ -18970,7 +18973,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="344" spans="1:16">
+    <row r="344" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A344" s="4" t="s">
         <v>952</v>
       </c>
@@ -18999,7 +19002,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="345" spans="1:16">
+    <row r="345" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A345" s="4" t="s">
         <v>954</v>
       </c>
@@ -19028,7 +19031,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="346" spans="1:16">
+    <row r="346" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A346" s="4" t="s">
         <v>958</v>
       </c>
@@ -19072,7 +19075,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="347" spans="1:16">
+    <row r="347" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A347" s="4" t="s">
         <v>960</v>
       </c>
@@ -19095,7 +19098,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="348" spans="1:16">
+    <row r="348" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A348" s="4" t="s">
         <v>962</v>
       </c>
@@ -19127,7 +19130,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="349" spans="1:16">
+    <row r="349" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A349" s="4" t="s">
         <v>964</v>
       </c>
@@ -19159,7 +19162,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="350" spans="1:16">
+    <row r="350" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A350" s="4" t="s">
         <v>966</v>
       </c>
@@ -19182,7 +19185,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="351" spans="1:16">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A351" s="4" t="s">
         <v>968</v>
       </c>
@@ -19211,7 +19214,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="352" spans="1:16">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A352" s="4" t="s">
         <v>970</v>
       </c>
@@ -19255,7 +19258,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="353" spans="1:16">
+    <row r="353" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A353" s="4" t="s">
         <v>972</v>
       </c>
@@ -19284,7 +19287,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="354" spans="1:16">
+    <row r="354" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A354" s="4" t="s">
         <v>974</v>
       </c>
@@ -19322,7 +19325,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="355" spans="1:16">
+    <row r="355" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A355" s="4" t="s">
         <v>976</v>
       </c>
@@ -19360,7 +19363,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="356" spans="1:16">
+    <row r="356" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A356" s="4" t="s">
         <v>978</v>
       </c>
@@ -19395,7 +19398,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="357" spans="1:16">
+    <row r="357" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A357" s="4" t="s">
         <v>980</v>
       </c>
@@ -19427,7 +19430,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="358" spans="1:16">
+    <row r="358" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A358" s="4" t="s">
         <v>982</v>
       </c>
@@ -19450,7 +19453,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="359" spans="1:16">
+    <row r="359" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A359" s="4" t="s">
         <v>984</v>
       </c>
@@ -19479,7 +19482,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="360" spans="1:16">
+    <row r="360" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A360" s="4" t="s">
         <v>986</v>
       </c>
@@ -19508,7 +19511,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="361" spans="1:16">
+    <row r="361" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A361" s="4" t="s">
         <v>988</v>
       </c>
@@ -19537,7 +19540,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="362" spans="1:16">
+    <row r="362" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A362" s="4" t="s">
         <v>990</v>
       </c>
@@ -19566,7 +19569,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="363" spans="1:16">
+    <row r="363" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A363" s="4" t="s">
         <v>992</v>
       </c>
@@ -19595,7 +19598,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="364" spans="1:16">
+    <row r="364" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A364" s="4" t="s">
         <v>994</v>
       </c>
@@ -19639,7 +19642,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="365" spans="1:16">
+    <row r="365" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A365" s="4" t="s">
         <v>996</v>
       </c>
@@ -19677,7 +19680,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="366" spans="1:16">
+    <row r="366" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A366" s="4" t="s">
         <v>1001</v>
       </c>
@@ -19721,7 +19724,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="367" spans="1:16">
+    <row r="367" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A367" s="4" t="s">
         <v>1003</v>
       </c>
@@ -19750,7 +19753,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="368" spans="1:16">
+    <row r="368" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A368" s="4" t="s">
         <v>1005</v>
       </c>
@@ -19779,7 +19782,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="369" spans="1:16">
+    <row r="369" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A369" s="4" t="s">
         <v>1007</v>
       </c>
@@ -19808,7 +19811,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="370" spans="1:16">
+    <row r="370" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A370" s="4" t="s">
         <v>1009</v>
       </c>
@@ -19837,7 +19840,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="371" spans="1:16">
+    <row r="371" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A371" s="4" t="s">
         <v>1011</v>
       </c>
@@ -19866,7 +19869,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="372" spans="1:16">
+    <row r="372" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A372" s="4" t="s">
         <v>1013</v>
       </c>
@@ -19889,7 +19892,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="373" spans="1:16">
+    <row r="373" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A373" s="4" t="s">
         <v>1015</v>
       </c>
@@ -19918,7 +19921,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="374" spans="1:16">
+    <row r="374" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A374" s="4" t="s">
         <v>1017</v>
       </c>
@@ -19947,7 +19950,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="375" spans="1:16">
+    <row r="375" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A375" s="4" t="s">
         <v>1019</v>
       </c>
@@ -19976,7 +19979,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="376" spans="1:16">
+    <row r="376" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A376" s="4" t="s">
         <v>1021</v>
       </c>
@@ -20005,7 +20008,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="377" spans="1:16">
+    <row r="377" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A377" s="4" t="s">
         <v>1023</v>
       </c>
@@ -20034,7 +20037,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="378" spans="1:16">
+    <row r="378" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A378" s="4" t="s">
         <v>1025</v>
       </c>
@@ -20066,7 +20069,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="379" spans="1:16">
+    <row r="379" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A379" s="4" t="s">
         <v>1027</v>
       </c>
@@ -20095,7 +20098,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="380" spans="1:16">
+    <row r="380" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A380" s="4" t="s">
         <v>1029</v>
       </c>
@@ -20118,7 +20121,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="381" spans="1:16">
+    <row r="381" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A381" s="4" t="s">
         <v>1031</v>
       </c>
@@ -20147,7 +20150,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="382" spans="1:16">
+    <row r="382" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A382" s="4" t="s">
         <v>1033</v>
       </c>
@@ -20170,7 +20173,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="383" spans="1:16">
+    <row r="383" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A383" s="4" t="s">
         <v>1035</v>
       </c>
@@ -20199,7 +20202,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="384" spans="1:16">
+    <row r="384" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A384" s="4" t="s">
         <v>1037</v>
       </c>
@@ -20228,7 +20231,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="385" spans="1:16">
+    <row r="385" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A385" s="4" t="s">
         <v>1039</v>
       </c>
@@ -20257,7 +20260,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="386" spans="1:16">
+    <row r="386" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A386" s="4" t="s">
         <v>1041</v>
       </c>
@@ -20286,7 +20289,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="387" spans="1:16">
+    <row r="387" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A387" s="4" t="s">
         <v>1043</v>
       </c>
@@ -20315,7 +20318,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="388" spans="1:16">
+    <row r="388" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A388" s="4" t="s">
         <v>1045</v>
       </c>
@@ -20338,7 +20341,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="389" spans="1:16">
+    <row r="389" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A389" s="4" t="s">
         <v>1047</v>
       </c>
@@ -20382,7 +20385,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="390" spans="1:16">
+    <row r="390" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A390" s="4" t="s">
         <v>1049</v>
       </c>
@@ -20411,7 +20414,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="391" spans="1:16">
+    <row r="391" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A391" s="4" t="s">
         <v>1051</v>
       </c>
@@ -20440,7 +20443,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="392" spans="1:16">
+    <row r="392" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A392" s="4" t="s">
         <v>1055</v>
       </c>
@@ -20469,7 +20472,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="393" spans="1:16">
+    <row r="393" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A393" s="4" t="s">
         <v>1057</v>
       </c>
@@ -20498,7 +20501,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="394" spans="1:16">
+    <row r="394" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A394" s="4" t="s">
         <v>1059</v>
       </c>
@@ -20521,7 +20524,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="395" spans="1:16">
+    <row r="395" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A395" s="4" t="s">
         <v>1063</v>
       </c>
@@ -20544,7 +20547,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="396" spans="1:16">
+    <row r="396" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A396" s="4" t="s">
         <v>1065</v>
       </c>
@@ -20573,7 +20576,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="397" spans="1:16">
+    <row r="397" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A397" s="4" t="s">
         <v>1067</v>
       </c>
@@ -20602,7 +20605,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="398" spans="1:16">
+    <row r="398" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A398" s="4" t="s">
         <v>1069</v>
       </c>
@@ -20646,7 +20649,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="399" spans="1:16">
+    <row r="399" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A399" s="4" t="s">
         <v>1071</v>
       </c>
@@ -20675,7 +20678,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="400" spans="1:16">
+    <row r="400" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A400" s="4" t="s">
         <v>1073</v>
       </c>
@@ -20704,7 +20707,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="401" spans="1:16">
+    <row r="401" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A401" s="4" t="s">
         <v>1075</v>
       </c>
@@ -20733,7 +20736,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="402" spans="1:16">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A402" s="4" t="s">
         <v>1077</v>
       </c>
@@ -20762,7 +20765,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="403" spans="1:16">
+    <row r="403" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A403" s="4" t="s">
         <v>1079</v>
       </c>
@@ -20791,7 +20794,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="404" spans="1:16">
+    <row r="404" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A404" s="4" t="s">
         <v>1081</v>
       </c>
@@ -20814,7 +20817,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="405" spans="1:16">
+    <row r="405" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A405" s="4" t="s">
         <v>1083</v>
       </c>
@@ -20855,7 +20858,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="406" spans="1:16">
+    <row r="406" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A406" s="4" t="s">
         <v>1089</v>
       </c>
@@ -20893,7 +20896,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="407" spans="1:16">
+    <row r="407" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A407" s="4" t="s">
         <v>1091</v>
       </c>
@@ -20934,7 +20937,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="408" spans="1:16">
+    <row r="408" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A408" s="4" t="s">
         <v>1093</v>
       </c>
@@ -20978,7 +20981,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="409" spans="1:16">
+    <row r="409" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A409" s="4" t="s">
         <v>1095</v>
       </c>
@@ -21007,7 +21010,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="410" spans="1:16">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A410" s="4" t="s">
         <v>1097</v>
       </c>
@@ -21039,7 +21042,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="411" spans="1:16">
+    <row r="411" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A411" s="4" t="s">
         <v>1099</v>
       </c>
@@ -21074,7 +21077,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="412" spans="1:16">
+    <row r="412" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A412" s="4" t="s">
         <v>1103</v>
       </c>
@@ -21118,7 +21121,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="413" spans="1:16">
+    <row r="413" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A413" s="4" t="s">
         <v>1105</v>
       </c>
@@ -21153,7 +21156,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="414" spans="1:16">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A414" s="4" t="s">
         <v>1107</v>
       </c>
@@ -21191,7 +21194,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="415" spans="1:16">
+    <row r="415" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A415" s="4" t="s">
         <v>1109</v>
       </c>
@@ -21235,7 +21238,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="416" spans="1:16">
+    <row r="416" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A416" s="4" t="s">
         <v>1111</v>
       </c>
@@ -21264,7 +21267,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="417" spans="1:16">
+    <row r="417" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A417" s="4" t="s">
         <v>1113</v>
       </c>
@@ -21308,7 +21311,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="418" spans="1:16">
+    <row r="418" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A418" s="4" t="s">
         <v>1117</v>
       </c>
@@ -21352,7 +21355,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="419" spans="1:16">
+    <row r="419" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A419" s="4" t="s">
         <v>1119</v>
       </c>
@@ -21396,7 +21399,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="420" spans="1:16">
+    <row r="420" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A420" s="4" t="s">
         <v>1121</v>
       </c>
@@ -21434,7 +21437,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="421" spans="1:16">
+    <row r="421" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A421" s="4" t="s">
         <v>1123</v>
       </c>
@@ -21478,7 +21481,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="422" spans="1:16">
+    <row r="422" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A422" s="4" t="s">
         <v>1125</v>
       </c>
@@ -21507,7 +21510,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="423" spans="1:16">
+    <row r="423" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A423" s="4" t="s">
         <v>1127</v>
       </c>
@@ -21536,7 +21539,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="424" spans="1:16">
+    <row r="424" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A424" s="4" t="s">
         <v>1129</v>
       </c>
@@ -21580,7 +21583,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="425" spans="1:16">
+    <row r="425" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A425" s="4" t="s">
         <v>1131</v>
       </c>
@@ -21609,7 +21612,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="426" spans="1:16">
+    <row r="426" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A426" s="4" t="s">
         <v>1133</v>
       </c>
@@ -21647,7 +21650,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="427" spans="1:16">
+    <row r="427" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A427" s="4" t="s">
         <v>1136</v>
       </c>
@@ -21685,7 +21688,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="428" spans="1:16">
+    <row r="428" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A428" s="4" t="s">
         <v>1138</v>
       </c>
@@ -21714,7 +21717,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="429" spans="1:16">
+    <row r="429" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A429" s="4" t="s">
         <v>1142</v>
       </c>
@@ -21737,7 +21740,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="430" spans="1:16">
+    <row r="430" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A430" s="4" t="s">
         <v>1144</v>
       </c>
@@ -21781,7 +21784,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="431" spans="1:16">
+    <row r="431" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A431" s="4" t="s">
         <v>1148</v>
       </c>
@@ -21813,7 +21816,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="432" spans="1:16">
+    <row r="432" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A432" s="4" t="s">
         <v>1150</v>
       </c>
@@ -21848,7 +21851,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="433" spans="1:16">
+    <row r="433" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A433" s="4" t="s">
         <v>1152</v>
       </c>
@@ -21877,7 +21880,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="434" spans="1:16">
+    <row r="434" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A434" s="4" t="s">
         <v>1154</v>
       </c>
@@ -21906,7 +21909,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="435" spans="1:16">
+    <row r="435" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A435" s="4" t="s">
         <v>1156</v>
       </c>
@@ -21950,7 +21953,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="436" spans="1:16">
+    <row r="436" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A436" s="4" t="s">
         <v>1158</v>
       </c>
@@ -21979,7 +21982,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="437" spans="1:16">
+    <row r="437" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A437" s="4" t="s">
         <v>1160</v>
       </c>
@@ -22036,15 +22039,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7312EB9-07A9-6641-ACD7-57F691F1F395}">
   <dimension ref="A1:E427"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="50.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.81640625" customWidth="1"/>
+    <col min="5" max="5" width="30.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -22061,7 +22064,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>111</v>
       </c>
@@ -22078,7 +22081,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>112</v>
       </c>
@@ -22095,7 +22098,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>113</v>
       </c>
@@ -22112,7 +22115,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>114</v>
       </c>
@@ -22129,7 +22132,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>115</v>
       </c>
@@ -22146,7 +22149,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>116</v>
       </c>
@@ -22163,7 +22166,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>119</v>
       </c>
@@ -22180,7 +22183,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>121</v>
       </c>
@@ -22197,7 +22200,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>122</v>
       </c>
@@ -22214,7 +22217,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>123</v>
       </c>
@@ -22231,7 +22234,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>124</v>
       </c>
@@ -22248,7 +22251,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>125</v>
       </c>
@@ -22265,7 +22268,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>126</v>
       </c>
@@ -22282,7 +22285,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>127</v>
       </c>
@@ -22299,7 +22302,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>128</v>
       </c>
@@ -22316,7 +22319,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>129</v>
       </c>
@@ -22333,7 +22336,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>130</v>
       </c>
@@ -22350,7 +22353,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>141</v>
       </c>
@@ -22367,7 +22370,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>142</v>
       </c>
@@ -22384,7 +22387,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>143</v>
       </c>
@@ -22401,7 +22404,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>144</v>
       </c>
@@ -22418,7 +22421,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>145</v>
       </c>
@@ -22435,7 +22438,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>146</v>
       </c>
@@ -22452,7 +22455,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>149</v>
       </c>
@@ -22469,7 +22472,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>150</v>
       </c>
@@ -22486,7 +22489,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>161</v>
       </c>
@@ -22503,7 +22506,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>162</v>
       </c>
@@ -22520,7 +22523,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>163</v>
       </c>
@@ -22537,7 +22540,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>164</v>
       </c>
@@ -22554,7 +22557,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>170</v>
       </c>
@@ -22571,7 +22574,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>210</v>
       </c>
@@ -22588,7 +22591,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>220</v>
       </c>
@@ -22605,7 +22608,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>230</v>
       </c>
@@ -22622,7 +22625,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>240</v>
       </c>
@@ -22639,7 +22642,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>311</v>
       </c>
@@ -22656,7 +22659,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>312</v>
       </c>
@@ -22673,7 +22676,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>321</v>
       </c>
@@ -22690,7 +22693,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>322</v>
       </c>
@@ -22707,7 +22710,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>9000</v>
       </c>
@@ -22724,7 +22727,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>9101</v>
       </c>
@@ -22741,7 +22744,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>9102</v>
       </c>
@@ -22758,7 +22761,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>9103</v>
       </c>
@@ -22775,7 +22778,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>9200</v>
       </c>
@@ -22792,7 +22795,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>9311</v>
       </c>
@@ -22809,7 +22812,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>9312</v>
       </c>
@@ -22826,7 +22829,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>9319</v>
       </c>
@@ -22843,7 +22846,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>9321</v>
       </c>
@@ -22860,7 +22863,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>9329</v>
       </c>
@@ -22877,7 +22880,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>9411</v>
       </c>
@@ -22894,7 +22897,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>9412</v>
       </c>
@@ -22911,7 +22914,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>9420</v>
       </c>
@@ -22928,7 +22931,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>9491</v>
       </c>
@@ -22945,7 +22948,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>9492</v>
       </c>
@@ -22962,7 +22965,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>9499</v>
       </c>
@@ -22979,7 +22982,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>9603</v>
       </c>
@@ -22996,7 +22999,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>9609</v>
       </c>
@@ -23013,7 +23016,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>9700</v>
       </c>
@@ -23030,7 +23033,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>9810</v>
       </c>
@@ -23047,7 +23050,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>9820</v>
       </c>
@@ -23064,7 +23067,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>4100</v>
       </c>
@@ -23081,7 +23084,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>4210</v>
       </c>
@@ -23098,7 +23101,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>4220</v>
       </c>
@@ -23115,7 +23118,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>4290</v>
       </c>
@@ -23132,7 +23135,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>4311</v>
       </c>
@@ -23149,7 +23152,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>4312</v>
       </c>
@@ -23166,7 +23169,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>4321</v>
       </c>
@@ -23183,7 +23186,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>4322</v>
       </c>
@@ -23200,7 +23203,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>4329</v>
       </c>
@@ -23217,7 +23220,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>4330</v>
       </c>
@@ -23234,7 +23237,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>4390</v>
       </c>
@@ -23251,7 +23254,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>202</v>
       </c>
@@ -23268,7 +23271,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>1010</v>
       </c>
@@ -23285,7 +23288,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>1020</v>
       </c>
@@ -23302,7 +23305,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>1030</v>
       </c>
@@ -23319,7 +23322,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>1040</v>
       </c>
@@ -23336,7 +23339,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>1050</v>
       </c>
@@ -23353,7 +23356,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>1061</v>
       </c>
@@ -23370,7 +23373,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>1062</v>
       </c>
@@ -23387,7 +23390,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>1071</v>
       </c>
@@ -23404,7 +23407,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>1072</v>
       </c>
@@ -23421,7 +23424,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>1073</v>
       </c>
@@ -23438,7 +23441,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>1074</v>
       </c>
@@ -23455,7 +23458,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>1075</v>
       </c>
@@ -23472,7 +23475,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>1079</v>
       </c>
@@ -23489,7 +23492,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>1080</v>
       </c>
@@ -23506,7 +23509,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>1101</v>
       </c>
@@ -23523,7 +23526,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>1102</v>
       </c>
@@ -23540,7 +23543,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>1103</v>
       </c>
@@ -23557,7 +23560,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>1104</v>
       </c>
@@ -23574,7 +23577,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>1200</v>
       </c>
@@ -23591,7 +23594,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>1311</v>
       </c>
@@ -23608,7 +23611,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>1312</v>
       </c>
@@ -23625,7 +23628,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>1313</v>
       </c>
@@ -23642,7 +23645,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>1391</v>
       </c>
@@ -23659,7 +23662,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>1392</v>
       </c>
@@ -23676,7 +23679,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>1393</v>
       </c>
@@ -23693,7 +23696,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>1394</v>
       </c>
@@ -23710,7 +23713,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>1399</v>
       </c>
@@ -23727,7 +23730,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>1410</v>
       </c>
@@ -23744,7 +23747,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>1420</v>
       </c>
@@ -23761,7 +23764,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>1430</v>
       </c>
@@ -23778,7 +23781,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>1511</v>
       </c>
@@ -23795,7 +23798,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>1512</v>
       </c>
@@ -23812,7 +23815,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>1520</v>
       </c>
@@ -23829,7 +23832,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>1610</v>
       </c>
@@ -23846,7 +23849,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>1621</v>
       </c>
@@ -23863,7 +23866,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>1622</v>
       </c>
@@ -23880,7 +23883,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>1623</v>
       </c>
@@ -23897,7 +23900,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>1629</v>
       </c>
@@ -23914,7 +23917,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>1701</v>
       </c>
@@ -23931,7 +23934,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>1702</v>
       </c>
@@ -23948,7 +23951,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>1709</v>
       </c>
@@ -23965,7 +23968,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>1811</v>
       </c>
@@ -23982,7 +23985,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>1812</v>
       </c>
@@ -23999,7 +24002,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>1820</v>
       </c>
@@ -24016,7 +24019,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>1910</v>
       </c>
@@ -24033,7 +24036,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>1920</v>
       </c>
@@ -24050,7 +24053,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>2011</v>
       </c>
@@ -24067,7 +24070,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>2012</v>
       </c>
@@ -24084,7 +24087,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>2013</v>
       </c>
@@ -24101,7 +24104,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>2021</v>
       </c>
@@ -24118,7 +24121,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>2022</v>
       </c>
@@ -24135,7 +24138,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>2023</v>
       </c>
@@ -24152,7 +24155,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>2029</v>
       </c>
@@ -24169,7 +24172,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>2030</v>
       </c>
@@ -24186,7 +24189,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>2100</v>
       </c>
@@ -24203,7 +24206,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>2211</v>
       </c>
@@ -24220,7 +24223,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>2219</v>
       </c>
@@ -24237,7 +24240,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>2220</v>
       </c>
@@ -24254,7 +24257,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>2310</v>
       </c>
@@ -24271,7 +24274,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>2391</v>
       </c>
@@ -24288,7 +24291,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>2392</v>
       </c>
@@ -24305,7 +24308,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>2393</v>
       </c>
@@ -24322,7 +24325,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>2394</v>
       </c>
@@ -24339,7 +24342,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>2395</v>
       </c>
@@ -24356,7 +24359,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>2396</v>
       </c>
@@ -24373,7 +24376,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>2399</v>
       </c>
@@ -24390,7 +24393,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>2410</v>
       </c>
@@ -24407,7 +24410,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>2420</v>
       </c>
@@ -24424,7 +24427,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>2431</v>
       </c>
@@ -24441,7 +24444,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>2432</v>
       </c>
@@ -24458,7 +24461,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>2511</v>
       </c>
@@ -24475,7 +24478,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>2512</v>
       </c>
@@ -24492,7 +24495,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>2513</v>
       </c>
@@ -24509,7 +24512,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>2520</v>
       </c>
@@ -24526,7 +24529,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>2591</v>
       </c>
@@ -24543,7 +24546,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>2592</v>
       </c>
@@ -24560,7 +24563,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>2593</v>
       </c>
@@ -24577,7 +24580,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>2599</v>
       </c>
@@ -24594,7 +24597,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>2610</v>
       </c>
@@ -24611,7 +24614,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>2620</v>
       </c>
@@ -24628,7 +24631,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>2630</v>
       </c>
@@ -24645,7 +24648,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>2640</v>
       </c>
@@ -24662,7 +24665,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>2651</v>
       </c>
@@ -24679,7 +24682,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>2652</v>
       </c>
@@ -24696,7 +24699,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>2660</v>
       </c>
@@ -24713,7 +24716,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>2670</v>
       </c>
@@ -24730,7 +24733,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>2680</v>
       </c>
@@ -24747,7 +24750,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>2710</v>
       </c>
@@ -24764,7 +24767,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>2720</v>
       </c>
@@ -24781,7 +24784,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>2731</v>
       </c>
@@ -24798,7 +24801,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>2732</v>
       </c>
@@ -24815,7 +24818,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>2733</v>
       </c>
@@ -24832,7 +24835,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>2740</v>
       </c>
@@ -24849,7 +24852,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>2750</v>
       </c>
@@ -24866,7 +24869,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>2790</v>
       </c>
@@ -24883,7 +24886,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>2811</v>
       </c>
@@ -24900,7 +24903,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>2812</v>
       </c>
@@ -24917,7 +24920,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>2813</v>
       </c>
@@ -24934,7 +24937,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>2814</v>
       </c>
@@ -24951,7 +24954,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>2815</v>
       </c>
@@ -24968,7 +24971,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>2816</v>
       </c>
@@ -24985,7 +24988,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>2817</v>
       </c>
@@ -25002,7 +25005,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>2818</v>
       </c>
@@ -25019,7 +25022,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>2819</v>
       </c>
@@ -25036,7 +25039,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>2821</v>
       </c>
@@ -25053,7 +25056,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>2822</v>
       </c>
@@ -25070,7 +25073,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>2823</v>
       </c>
@@ -25087,7 +25090,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>2824</v>
       </c>
@@ -25104,7 +25107,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>2825</v>
       </c>
@@ -25121,7 +25124,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>2826</v>
       </c>
@@ -25138,7 +25141,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>2829</v>
       </c>
@@ -25155,7 +25158,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>2910</v>
       </c>
@@ -25172,7 +25175,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>2920</v>
       </c>
@@ -25189,7 +25192,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>2930</v>
       </c>
@@ -25206,7 +25209,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>3011</v>
       </c>
@@ -25223,7 +25226,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>3012</v>
       </c>
@@ -25240,7 +25243,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>3020</v>
       </c>
@@ -25257,7 +25260,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>3030</v>
       </c>
@@ -25274,7 +25277,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>3040</v>
       </c>
@@ -25291,7 +25294,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>3091</v>
       </c>
@@ -25308,7 +25311,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>3092</v>
       </c>
@@ -25325,7 +25328,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>3099</v>
       </c>
@@ -25342,7 +25345,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>3100</v>
       </c>
@@ -25359,7 +25362,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>3211</v>
       </c>
@@ -25376,7 +25379,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>3212</v>
       </c>
@@ -25393,7 +25396,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>3220</v>
       </c>
@@ -25410,7 +25413,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>3230</v>
       </c>
@@ -25427,7 +25430,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>3240</v>
       </c>
@@ -25444,7 +25447,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>3250</v>
       </c>
@@ -25461,7 +25464,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>3290</v>
       </c>
@@ -25478,7 +25481,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>3311</v>
       </c>
@@ -25495,7 +25498,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>3312</v>
       </c>
@@ -25512,7 +25515,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>3313</v>
       </c>
@@ -25529,7 +25532,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>3314</v>
       </c>
@@ -25546,7 +25549,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>3315</v>
       </c>
@@ -25563,7 +25566,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>3319</v>
       </c>
@@ -25580,7 +25583,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>3320</v>
       </c>
@@ -25597,7 +25600,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>477</v>
       </c>
@@ -25614,7 +25617,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>478</v>
       </c>
@@ -25631,7 +25634,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>479</v>
       </c>
@@ -25648,7 +25651,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>492</v>
       </c>
@@ -25665,7 +25668,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>4510</v>
       </c>
@@ -25682,7 +25685,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>4520</v>
       </c>
@@ -25699,7 +25702,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>4530</v>
       </c>
@@ -25716,7 +25719,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>4540</v>
       </c>
@@ -25733,7 +25736,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>4610</v>
       </c>
@@ -25750,7 +25753,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>4620</v>
       </c>
@@ -25767,7 +25770,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>4630</v>
       </c>
@@ -25784,7 +25787,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>4641</v>
       </c>
@@ -25801,7 +25804,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>4649</v>
       </c>
@@ -25818,7 +25821,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>4651</v>
       </c>
@@ -25835,7 +25838,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>4652</v>
       </c>
@@ -25852,7 +25855,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>4653</v>
       </c>
@@ -25869,7 +25872,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>4659</v>
       </c>
@@ -25886,7 +25889,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>4661</v>
       </c>
@@ -25903,7 +25906,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>4662</v>
       </c>
@@ -25920,7 +25923,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="229" spans="1:5">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>4663</v>
       </c>
@@ -25937,7 +25940,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>4669</v>
       </c>
@@ -25954,7 +25957,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="231" spans="1:5">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>4690</v>
       </c>
@@ -25971,7 +25974,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>4711</v>
       </c>
@@ -25988,7 +25991,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="233" spans="1:5">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>4719</v>
       </c>
@@ -26005,7 +26008,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>4721</v>
       </c>
@@ -26022,7 +26025,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>4722</v>
       </c>
@@ -26039,7 +26042,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>4723</v>
       </c>
@@ -26056,7 +26059,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="237" spans="1:5">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>4730</v>
       </c>
@@ -26073,7 +26076,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>4741</v>
       </c>
@@ -26090,7 +26093,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="239" spans="1:5">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>4742</v>
       </c>
@@ -26107,7 +26110,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="240" spans="1:5">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>4751</v>
       </c>
@@ -26124,7 +26127,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>4752</v>
       </c>
@@ -26141,7 +26144,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="242" spans="1:5">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>4753</v>
       </c>
@@ -26158,7 +26161,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="243" spans="1:5">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>4759</v>
       </c>
@@ -26175,7 +26178,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="244" spans="1:5">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>4761</v>
       </c>
@@ -26192,7 +26195,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="245" spans="1:5">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>4762</v>
       </c>
@@ -26209,7 +26212,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="246" spans="1:5">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>4763</v>
       </c>
@@ -26226,7 +26229,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="247" spans="1:5">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>4764</v>
       </c>
@@ -26243,7 +26246,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="248" spans="1:5">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>4771</v>
       </c>
@@ -26260,7 +26263,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="249" spans="1:5">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>4772</v>
       </c>
@@ -26277,7 +26280,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="250" spans="1:5">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>4773</v>
       </c>
@@ -26294,7 +26297,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="251" spans="1:5">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>4774</v>
       </c>
@@ -26311,7 +26314,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="252" spans="1:5">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>4781</v>
       </c>
@@ -26328,7 +26331,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="253" spans="1:5">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>4782</v>
       </c>
@@ -26345,7 +26348,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="254" spans="1:5">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>4789</v>
       </c>
@@ -26362,7 +26365,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="255" spans="1:5">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>4791</v>
       </c>
@@ -26379,7 +26382,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="256" spans="1:5">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>4799</v>
       </c>
@@ -26396,7 +26399,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>4911</v>
       </c>
@@ -26413,7 +26416,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="258" spans="1:5">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>4912</v>
       </c>
@@ -26430,7 +26433,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="259" spans="1:5">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>4921</v>
       </c>
@@ -26447,7 +26450,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="260" spans="1:5">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>4922</v>
       </c>
@@ -26464,7 +26467,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="261" spans="1:5">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>4923</v>
       </c>
@@ -26481,7 +26484,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="262" spans="1:5">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>4930</v>
       </c>
@@ -26498,7 +26501,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>5011</v>
       </c>
@@ -26515,7 +26518,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="264" spans="1:5">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>5012</v>
       </c>
@@ -26532,7 +26535,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="265" spans="1:5">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>5021</v>
       </c>
@@ -26549,7 +26552,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="266" spans="1:5">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>5022</v>
       </c>
@@ -26566,7 +26569,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="267" spans="1:5">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>5110</v>
       </c>
@@ -26583,7 +26586,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="268" spans="1:5">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>5120</v>
       </c>
@@ -26600,7 +26603,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="269" spans="1:5">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>5210</v>
       </c>
@@ -26617,7 +26620,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="270" spans="1:5">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>5221</v>
       </c>
@@ -26634,7 +26637,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="271" spans="1:5">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>5222</v>
       </c>
@@ -26651,7 +26654,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>5223</v>
       </c>
@@ -26668,7 +26671,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="273" spans="1:5">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>5224</v>
       </c>
@@ -26685,7 +26688,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="274" spans="1:5">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>5229</v>
       </c>
@@ -26702,7 +26705,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="275" spans="1:5">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>5310</v>
       </c>
@@ -26719,7 +26722,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="276" spans="1:5">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>5320</v>
       </c>
@@ -26736,7 +26739,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="277" spans="1:5">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>5510</v>
       </c>
@@ -26753,7 +26756,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="278" spans="1:5">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>5520</v>
       </c>
@@ -26770,7 +26773,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="279" spans="1:5">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>5590</v>
       </c>
@@ -26787,7 +26790,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="280" spans="1:5">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>5610</v>
       </c>
@@ -26804,7 +26807,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="281" spans="1:5">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>5621</v>
       </c>
@@ -26821,7 +26824,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="282" spans="1:5">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>5629</v>
       </c>
@@ -26838,7 +26841,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="283" spans="1:5">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>5630</v>
       </c>
@@ -26855,7 +26858,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="284" spans="1:5">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>5811</v>
       </c>
@@ -26872,7 +26875,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="285" spans="1:5">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>5812</v>
       </c>
@@ -26889,7 +26892,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="286" spans="1:5">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>5813</v>
       </c>
@@ -26906,7 +26909,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="287" spans="1:5">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>5819</v>
       </c>
@@ -26923,7 +26926,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="288" spans="1:5">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>5820</v>
       </c>
@@ -26940,7 +26943,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="289" spans="1:5">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>5911</v>
       </c>
@@ -26957,7 +26960,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="290" spans="1:5">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>5912</v>
       </c>
@@ -26974,7 +26977,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="291" spans="1:5">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>5913</v>
       </c>
@@ -26991,7 +26994,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="292" spans="1:5">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>5914</v>
       </c>
@@ -27008,7 +27011,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="293" spans="1:5">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>5920</v>
       </c>
@@ -27025,7 +27028,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="294" spans="1:5">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A294">
         <v>6010</v>
       </c>
@@ -27042,7 +27045,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="295" spans="1:5">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A295">
         <v>6020</v>
       </c>
@@ -27059,7 +27062,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="296" spans="1:5">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A296">
         <v>6110</v>
       </c>
@@ -27076,7 +27079,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="297" spans="1:5">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>6120</v>
       </c>
@@ -27093,7 +27096,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="298" spans="1:5">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>6130</v>
       </c>
@@ -27110,7 +27113,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="299" spans="1:5">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>6190</v>
       </c>
@@ -27127,7 +27130,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="300" spans="1:5">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>6201</v>
       </c>
@@ -27144,7 +27147,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="301" spans="1:5">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>6202</v>
       </c>
@@ -27161,7 +27164,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="302" spans="1:5">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>6209</v>
       </c>
@@ -27178,7 +27181,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="303" spans="1:5">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>6311</v>
       </c>
@@ -27195,7 +27198,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="304" spans="1:5">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>6312</v>
       </c>
@@ -27212,7 +27215,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="305" spans="1:5">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>6391</v>
       </c>
@@ -27229,7 +27232,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="306" spans="1:5">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>6399</v>
       </c>
@@ -27246,7 +27249,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="307" spans="1:5">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>6411</v>
       </c>
@@ -27263,7 +27266,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="308" spans="1:5">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>6419</v>
       </c>
@@ -27280,7 +27283,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="309" spans="1:5">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>6420</v>
       </c>
@@ -27297,7 +27300,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="310" spans="1:5">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>6430</v>
       </c>
@@ -27314,7 +27317,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="311" spans="1:5">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>6491</v>
       </c>
@@ -27331,7 +27334,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="312" spans="1:5">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>6492</v>
       </c>
@@ -27348,7 +27351,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="313" spans="1:5">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>6499</v>
       </c>
@@ -27365,7 +27368,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="314" spans="1:5">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>6511</v>
       </c>
@@ -27382,7 +27385,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="315" spans="1:5">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>6512</v>
       </c>
@@ -27399,7 +27402,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="316" spans="1:5">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>6520</v>
       </c>
@@ -27416,7 +27419,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="317" spans="1:5">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>6530</v>
       </c>
@@ -27433,7 +27436,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="318" spans="1:5">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A318">
         <v>6611</v>
       </c>
@@ -27450,7 +27453,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="319" spans="1:5">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A319">
         <v>6612</v>
       </c>
@@ -27467,7 +27470,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="320" spans="1:5">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A320">
         <v>6619</v>
       </c>
@@ -27484,7 +27487,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="321" spans="1:5">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>6621</v>
       </c>
@@ -27501,7 +27504,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="322" spans="1:5">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>6622</v>
       </c>
@@ -27518,7 +27521,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="323" spans="1:5">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>6629</v>
       </c>
@@ -27535,7 +27538,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="324" spans="1:5">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>6630</v>
       </c>
@@ -27552,7 +27555,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="325" spans="1:5">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A325">
         <v>6810</v>
       </c>
@@ -27569,7 +27572,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="326" spans="1:5">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A326">
         <v>6820</v>
       </c>
@@ -27586,7 +27589,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="327" spans="1:5">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A327">
         <v>6910</v>
       </c>
@@ -27603,7 +27606,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="328" spans="1:5">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A328">
         <v>6920</v>
       </c>
@@ -27620,7 +27623,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="329" spans="1:5">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A329">
         <v>7010</v>
       </c>
@@ -27637,7 +27640,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="330" spans="1:5">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A330">
         <v>7020</v>
       </c>
@@ -27654,7 +27657,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="331" spans="1:5">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A331">
         <v>7110</v>
       </c>
@@ -27671,7 +27674,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="332" spans="1:5">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A332">
         <v>7120</v>
       </c>
@@ -27688,7 +27691,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="333" spans="1:5">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A333">
         <v>7210</v>
       </c>
@@ -27705,7 +27708,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="334" spans="1:5">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A334">
         <v>7220</v>
       </c>
@@ -27722,7 +27725,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="335" spans="1:5">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A335">
         <v>7310</v>
       </c>
@@ -27739,7 +27742,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="336" spans="1:5">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A336">
         <v>7320</v>
       </c>
@@ -27756,7 +27759,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="337" spans="1:5">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A337">
         <v>7410</v>
       </c>
@@ -27773,7 +27776,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="338" spans="1:5">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A338">
         <v>7420</v>
       </c>
@@ -27790,7 +27793,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="339" spans="1:5">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A339">
         <v>7490</v>
       </c>
@@ -27807,7 +27810,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="340" spans="1:5">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A340">
         <v>7500</v>
       </c>
@@ -27824,7 +27827,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="341" spans="1:5">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A341">
         <v>7710</v>
       </c>
@@ -27841,7 +27844,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="342" spans="1:5">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A342">
         <v>7721</v>
       </c>
@@ -27858,7 +27861,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="343" spans="1:5">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A343">
         <v>7722</v>
       </c>
@@ -27875,7 +27878,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="344" spans="1:5">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A344">
         <v>7729</v>
       </c>
@@ -27892,7 +27895,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="345" spans="1:5">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A345">
         <v>7730</v>
       </c>
@@ -27909,7 +27912,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="346" spans="1:5">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A346">
         <v>7740</v>
       </c>
@@ -27926,7 +27929,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="347" spans="1:5">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A347">
         <v>7810</v>
       </c>
@@ -27943,7 +27946,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="348" spans="1:5">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A348">
         <v>7820</v>
       </c>
@@ -27960,7 +27963,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="349" spans="1:5">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A349">
         <v>7830</v>
       </c>
@@ -27977,7 +27980,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="350" spans="1:5">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A350">
         <v>7911</v>
       </c>
@@ -27994,7 +27997,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="351" spans="1:5">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A351">
         <v>7912</v>
       </c>
@@ -28011,7 +28014,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="352" spans="1:5">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A352">
         <v>7990</v>
       </c>
@@ -28028,7 +28031,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="353" spans="1:5">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A353">
         <v>8010</v>
       </c>
@@ -28045,7 +28048,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="354" spans="1:5">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A354">
         <v>8020</v>
       </c>
@@ -28062,7 +28065,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="355" spans="1:5">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A355">
         <v>8030</v>
       </c>
@@ -28079,7 +28082,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="356" spans="1:5">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A356">
         <v>8110</v>
       </c>
@@ -28096,7 +28099,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="357" spans="1:5">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A357">
         <v>8121</v>
       </c>
@@ -28113,7 +28116,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="358" spans="1:5">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A358">
         <v>8129</v>
       </c>
@@ -28130,7 +28133,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="359" spans="1:5">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A359">
         <v>8130</v>
       </c>
@@ -28147,7 +28150,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="360" spans="1:5">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A360">
         <v>8211</v>
       </c>
@@ -28164,7 +28167,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="361" spans="1:5">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A361">
         <v>8219</v>
       </c>
@@ -28181,7 +28184,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="362" spans="1:5">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A362">
         <v>8220</v>
       </c>
@@ -28198,7 +28201,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="363" spans="1:5">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A363">
         <v>8230</v>
       </c>
@@ -28215,7 +28218,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="364" spans="1:5">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A364">
         <v>8291</v>
       </c>
@@ -28232,7 +28235,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="365" spans="1:5">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A365">
         <v>8292</v>
       </c>
@@ -28249,7 +28252,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="366" spans="1:5">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A366">
         <v>8299</v>
       </c>
@@ -28266,7 +28269,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="367" spans="1:5">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A367">
         <v>9511</v>
       </c>
@@ -28283,7 +28286,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="368" spans="1:5">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A368">
         <v>9512</v>
       </c>
@@ -28300,7 +28303,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="369" spans="1:5">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A369">
         <v>9521</v>
       </c>
@@ -28317,7 +28320,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="370" spans="1:5">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A370">
         <v>9522</v>
       </c>
@@ -28334,7 +28337,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="371" spans="1:5">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A371">
         <v>9523</v>
       </c>
@@ -28351,7 +28354,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="372" spans="1:5">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A372">
         <v>9524</v>
       </c>
@@ -28368,7 +28371,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="373" spans="1:5">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A373">
         <v>9529</v>
       </c>
@@ -28385,7 +28388,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="374" spans="1:5">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A374">
         <v>9601</v>
       </c>
@@ -28402,7 +28405,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="375" spans="1:5">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A375">
         <v>9602</v>
       </c>
@@ -28419,7 +28422,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="376" spans="1:5">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A376">
         <v>510</v>
       </c>
@@ -28436,7 +28439,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="377" spans="1:5">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A377">
         <v>520</v>
       </c>
@@ -28453,7 +28456,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="378" spans="1:5">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A378">
         <v>610</v>
       </c>
@@ -28470,7 +28473,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="379" spans="1:5">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A379">
         <v>620</v>
       </c>
@@ -28487,7 +28490,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="380" spans="1:5">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A380">
         <v>663</v>
       </c>
@@ -28504,7 +28507,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="381" spans="1:5">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A381">
         <v>710</v>
       </c>
@@ -28521,7 +28524,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="382" spans="1:5">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A382">
         <v>721</v>
       </c>
@@ -28538,7 +28541,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="383" spans="1:5">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A383">
         <v>729</v>
       </c>
@@ -28555,7 +28558,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="384" spans="1:5">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A384">
         <v>810</v>
       </c>
@@ -28572,7 +28575,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="385" spans="1:5">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A385">
         <v>891</v>
       </c>
@@ -28589,7 +28592,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="386" spans="1:5">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A386">
         <v>892</v>
       </c>
@@ -28606,7 +28609,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="387" spans="1:5">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A387">
         <v>893</v>
       </c>
@@ -28623,7 +28626,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="388" spans="1:5">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A388">
         <v>899</v>
       </c>
@@ -28640,7 +28643,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="389" spans="1:5">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A389">
         <v>910</v>
       </c>
@@ -28657,7 +28660,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="390" spans="1:5">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A390">
         <v>932</v>
       </c>
@@ -28674,7 +28677,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="391" spans="1:5">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A391">
         <v>990</v>
       </c>
@@ -28691,7 +28694,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="392" spans="1:5">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A392">
         <v>3510</v>
       </c>
@@ -28708,7 +28711,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="393" spans="1:5">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A393">
         <v>3520</v>
       </c>
@@ -28725,7 +28728,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="394" spans="1:5">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A394">
         <v>3530</v>
       </c>
@@ -28742,7 +28745,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="395" spans="1:5">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A395">
         <v>3600</v>
       </c>
@@ -28759,7 +28762,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="396" spans="1:5">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A396">
         <v>3700</v>
       </c>
@@ -28776,7 +28779,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="397" spans="1:5">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A397">
         <v>3811</v>
       </c>
@@ -28793,7 +28796,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="398" spans="1:5">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A398">
         <v>3812</v>
       </c>
@@ -28810,7 +28813,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="399" spans="1:5">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A399">
         <v>3821</v>
       </c>
@@ -28827,7 +28830,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="400" spans="1:5">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A400">
         <v>3822</v>
       </c>
@@ -28844,7 +28847,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="401" spans="1:5">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A401">
         <v>3830</v>
       </c>
@@ -28861,7 +28864,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="402" spans="1:5">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A402">
         <v>3900</v>
       </c>
@@ -28878,7 +28881,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="403" spans="1:5">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A403">
         <v>8411</v>
       </c>
@@ -28895,7 +28898,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="404" spans="1:5">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A404">
         <v>8412</v>
       </c>
@@ -28912,7 +28915,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="405" spans="1:5">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A405">
         <v>8413</v>
       </c>
@@ -28929,7 +28932,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="406" spans="1:5">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A406">
         <v>8421</v>
       </c>
@@ -28946,7 +28949,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="407" spans="1:5">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A407">
         <v>8422</v>
       </c>
@@ -28963,7 +28966,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="408" spans="1:5">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A408">
         <v>8423</v>
       </c>
@@ -28980,7 +28983,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="409" spans="1:5">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A409">
         <v>8430</v>
       </c>
@@ -28997,7 +29000,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="410" spans="1:5">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A410">
         <v>8510</v>
       </c>
@@ -29014,7 +29017,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="411" spans="1:5">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A411">
         <v>8521</v>
       </c>
@@ -29031,7 +29034,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="412" spans="1:5">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A412">
         <v>8522</v>
       </c>
@@ -29048,7 +29051,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="413" spans="1:5">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A413">
         <v>8530</v>
       </c>
@@ -29065,7 +29068,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="414" spans="1:5">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A414">
         <v>8541</v>
       </c>
@@ -29082,7 +29085,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="415" spans="1:5">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A415">
         <v>8542</v>
       </c>
@@ -29099,7 +29102,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="416" spans="1:5">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A416">
         <v>8549</v>
       </c>
@@ -29116,7 +29119,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="417" spans="1:5">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A417">
         <v>8550</v>
       </c>
@@ -29133,7 +29136,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="418" spans="1:5">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A418">
         <v>8610</v>
       </c>
@@ -29150,7 +29153,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="419" spans="1:5">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A419">
         <v>8620</v>
       </c>
@@ -29167,7 +29170,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="420" spans="1:5">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A420">
         <v>8690</v>
       </c>
@@ -29184,7 +29187,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="421" spans="1:5">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A421">
         <v>8710</v>
       </c>
@@ -29201,7 +29204,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="422" spans="1:5">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A422">
         <v>8720</v>
       </c>
@@ -29218,7 +29221,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="423" spans="1:5">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A423">
         <v>8730</v>
       </c>
@@ -29235,7 +29238,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="424" spans="1:5">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A424">
         <v>8790</v>
       </c>
@@ -29252,7 +29255,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="425" spans="1:5">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A425">
         <v>8810</v>
       </c>
@@ -29269,7 +29272,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="426" spans="1:5">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A426">
         <v>8890</v>
       </c>
@@ -29286,7 +29289,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="427" spans="1:5">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A427">
         <v>9900</v>
       </c>
@@ -29304,7 +29307,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:C427">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C427">
     <sortCondition ref="C23"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -29315,14 +29318,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2DEA81F-4F9F-7543-8D03-FF11F2C25C4A}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="44.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -29333,10 +29336,10 @@
         <v>1597</v>
       </c>
       <c r="D1" t="s">
-        <v>1622</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>5419</v>
       </c>
@@ -29350,7 +29353,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>9111</v>
       </c>
@@ -29364,7 +29367,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>5311</v>
       </c>
@@ -29378,7 +29381,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>6121</v>
       </c>
@@ -29392,7 +29395,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>9313</v>
       </c>
@@ -29406,7 +29409,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>5120</v>
       </c>
@@ -29420,7 +29423,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>9211</v>
       </c>
@@ -29434,7 +29437,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>9412</v>
       </c>
@@ -29448,7 +29451,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>5153</v>
       </c>
@@ -29462,7 +29465,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>9121</v>
       </c>
@@ -29476,7 +29479,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>9112</v>
       </c>
@@ -29490,7 +29493,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>9212</v>
       </c>
@@ -29504,7 +29507,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>7114</v>
       </c>
@@ -29518,7 +29521,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>5322</v>
       </c>
@@ -29532,7 +29535,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>7413</v>
       </c>
@@ -29546,7 +29549,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>7115</v>
       </c>
@@ -29560,7 +29563,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>9129</v>
       </c>
@@ -29574,7 +29577,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>7131</v>
       </c>
@@ -29588,7 +29591,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>5161</v>
       </c>
@@ -29602,7 +29605,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>9329</v>
       </c>
@@ -29616,7 +29619,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>9213</v>
       </c>
@@ -29630,7 +29633,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>9333</v>
       </c>
@@ -29644,7 +29647,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>9624</v>
       </c>
@@ -29658,7 +29661,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>7111</v>
       </c>
@@ -29672,7 +29675,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>9312</v>
       </c>

--- a/Data/Excel/NLFS_III/Sanjeet_classification.xlsx
+++ b/Data/Excel/NLFS_III/Sanjeet_classification.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10709"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Formal_Informal_wage\Data\Excel\NLFS_III\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandeepsharma/Desktop/Research/Data Analysis/Formal Informal wage/Formal_Informal_wage/Data/Excel/NLFS_III/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228E3919-CE71-4005-AD81-3E56183F5B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{74E8EA6C-B9E8-744E-9975-27A5F7FCA523}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27320" windowHeight="14860" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="education_III" sheetId="1" r:id="rId1"/>
@@ -4907,7 +4907,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -5252,13 +5252,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultColWidth="11.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="22.81640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.1796875" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5286,7 +5286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5300,7 +5300,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5314,7 +5314,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -5356,7 +5356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -5370,7 +5370,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -5384,7 +5384,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -5398,7 +5398,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -5426,7 +5426,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -5454,7 +5454,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -5496,7 +5496,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -5510,7 +5510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -5537,15 +5537,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F131"/>
-  <sheetFormatPr defaultColWidth="11.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="22.36328125" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" customWidth="1"/>
-    <col min="5" max="5" width="18.453125" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5565,7 +5565,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="16">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5585,7 +5585,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="16">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5605,7 +5605,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="16">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5625,7 +5625,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="16">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5645,7 +5645,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="16">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5665,7 +5665,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="16">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5685,7 +5685,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="16">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="16">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="16">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="16">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="16">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="16">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5805,7 +5805,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="16">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="16">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5865,7 +5865,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="16">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5885,7 +5885,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="16">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5905,7 +5905,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="16">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5925,7 +5925,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="16">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5945,7 +5945,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="16">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5965,7 +5965,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="16">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="16">
       <c r="A23">
         <v>22</v>
       </c>
@@ -6005,7 +6005,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="16">
       <c r="A24">
         <v>23</v>
       </c>
@@ -6025,7 +6025,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="16">
       <c r="A25">
         <v>24</v>
       </c>
@@ -6045,7 +6045,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="16">
       <c r="A26">
         <v>25</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="16">
       <c r="A27">
         <v>26</v>
       </c>
@@ -6085,7 +6085,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="16">
       <c r="A28">
         <v>27</v>
       </c>
@@ -6105,7 +6105,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="16">
       <c r="A29">
         <v>28</v>
       </c>
@@ -6125,7 +6125,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="16">
       <c r="A30">
         <v>29</v>
       </c>
@@ -6145,7 +6145,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="16">
       <c r="A31">
         <v>30</v>
       </c>
@@ -6165,7 +6165,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="16">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6185,7 +6185,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="16">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="16">
       <c r="A34">
         <v>33</v>
       </c>
@@ -6225,7 +6225,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="16">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6245,7 +6245,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="16">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6265,7 +6265,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="16">
       <c r="A37">
         <v>36</v>
       </c>
@@ -6285,7 +6285,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="16">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" ht="16">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6325,7 +6325,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" ht="16">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6345,7 +6345,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" ht="16">
       <c r="A41">
         <v>40</v>
       </c>
@@ -6365,7 +6365,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" ht="16">
       <c r="A42">
         <v>41</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" ht="16">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="16">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6425,7 +6425,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" ht="16">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6445,7 +6445,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" ht="16">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6465,7 +6465,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" ht="16">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6485,7 +6485,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" ht="16">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="16">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6525,7 +6525,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" ht="16">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6545,7 +6545,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" ht="16">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6565,7 +6565,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" ht="16">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6585,7 +6585,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="16">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6605,7 +6605,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" ht="16">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" ht="16">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" ht="16">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" ht="16">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6685,7 +6685,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" ht="16">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6705,7 +6705,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" ht="16">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6725,7 +6725,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" ht="16">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" ht="16">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6765,7 +6765,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" ht="16">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="16">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6805,7 +6805,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" ht="16">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6825,7 +6825,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" ht="16">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6845,7 +6845,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" ht="16">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6865,7 +6865,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" ht="16">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" ht="16">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" ht="16">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" ht="16">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6945,7 +6945,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" ht="16">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6965,7 +6965,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" ht="16">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="16">
       <c r="A73">
         <v>72</v>
       </c>
@@ -7005,7 +7005,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" ht="16">
       <c r="A74">
         <v>73</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" ht="16">
       <c r="A75">
         <v>74</v>
       </c>
@@ -7045,7 +7045,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" ht="16">
       <c r="A76">
         <v>75</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" ht="16">
       <c r="A77">
         <v>76</v>
       </c>
@@ -7085,7 +7085,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" ht="16">
       <c r="A78">
         <v>77</v>
       </c>
@@ -7105,7 +7105,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" ht="16">
       <c r="A79">
         <v>78</v>
       </c>
@@ -7125,7 +7125,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" ht="16">
       <c r="A80">
         <v>79</v>
       </c>
@@ -7145,7 +7145,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" ht="16">
       <c r="A81">
         <v>80</v>
       </c>
@@ -7165,7 +7165,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" ht="16">
       <c r="A82">
         <v>81</v>
       </c>
@@ -7185,7 +7185,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" ht="16">
       <c r="A83">
         <v>83</v>
       </c>
@@ -7205,7 +7205,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" ht="16">
       <c r="A84">
         <v>84</v>
       </c>
@@ -7225,7 +7225,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" ht="16">
       <c r="A85">
         <v>85</v>
       </c>
@@ -7245,7 +7245,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" ht="16">
       <c r="A86">
         <v>86</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" ht="16">
       <c r="A87">
         <v>87</v>
       </c>
@@ -7285,7 +7285,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" ht="16">
       <c r="A88">
         <v>88</v>
       </c>
@@ -7305,7 +7305,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" ht="16">
       <c r="A89">
         <v>89</v>
       </c>
@@ -7325,7 +7325,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" ht="16">
       <c r="A90">
         <v>90</v>
       </c>
@@ -7345,7 +7345,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" ht="16">
       <c r="A91">
         <v>91</v>
       </c>
@@ -7365,7 +7365,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" ht="16">
       <c r="A92">
         <v>92</v>
       </c>
@@ -7385,7 +7385,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" ht="16">
       <c r="A93">
         <v>93</v>
       </c>
@@ -7405,7 +7405,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" ht="16">
       <c r="A94">
         <v>94</v>
       </c>
@@ -7425,7 +7425,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" ht="16">
       <c r="A95">
         <v>96</v>
       </c>
@@ -7445,7 +7445,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" ht="16">
       <c r="A96">
         <v>97</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" ht="16">
       <c r="A97">
         <v>98</v>
       </c>
@@ -7485,7 +7485,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" ht="16">
       <c r="A98">
         <v>99</v>
       </c>
@@ -7505,7 +7505,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" ht="16">
       <c r="A99">
         <v>100</v>
       </c>
@@ -7525,7 +7525,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" ht="16">
       <c r="A100">
         <v>110</v>
       </c>
@@ -7545,7 +7545,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" ht="16">
       <c r="A101">
         <v>115</v>
       </c>
@@ -7565,7 +7565,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" ht="16">
       <c r="A102">
         <v>116</v>
       </c>
@@ -7585,7 +7585,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" ht="16">
       <c r="A103">
         <v>117</v>
       </c>
@@ -7605,7 +7605,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" ht="16">
       <c r="A104">
         <v>118</v>
       </c>
@@ -7625,7 +7625,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" ht="16">
       <c r="A105">
         <v>119</v>
       </c>
@@ -7645,7 +7645,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" ht="16">
       <c r="A106">
         <v>120</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" ht="16">
       <c r="A107">
         <v>121</v>
       </c>
@@ -7685,7 +7685,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" ht="16">
       <c r="A108">
         <v>122</v>
       </c>
@@ -7705,7 +7705,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" ht="16">
       <c r="A109">
         <v>123</v>
       </c>
@@ -7725,7 +7725,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" ht="16">
       <c r="A110">
         <v>124</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" ht="16">
       <c r="A111">
         <v>125</v>
       </c>
@@ -7765,7 +7765,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" ht="16">
       <c r="A112">
         <v>126</v>
       </c>
@@ -7785,7 +7785,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" ht="16">
       <c r="A113">
         <v>127</v>
       </c>
@@ -7805,7 +7805,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" ht="16">
       <c r="A114">
         <v>128</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" ht="16">
       <c r="A115">
         <v>129</v>
       </c>
@@ -7845,7 +7845,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" ht="16">
       <c r="A116">
         <v>130</v>
       </c>
@@ -7865,7 +7865,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" ht="16">
       <c r="A117">
         <v>131</v>
       </c>
@@ -7885,7 +7885,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" ht="16">
       <c r="A118">
         <v>132</v>
       </c>
@@ -7905,7 +7905,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" ht="16">
       <c r="A119">
         <v>133</v>
       </c>
@@ -7925,7 +7925,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" ht="16">
       <c r="A120">
         <v>134</v>
       </c>
@@ -7945,7 +7945,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" ht="16">
       <c r="A121">
         <v>135</v>
       </c>
@@ -7965,7 +7965,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" ht="16">
       <c r="A122">
         <v>136</v>
       </c>
@@ -7985,7 +7985,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" ht="16">
       <c r="A123">
         <v>137</v>
       </c>
@@ -8005,7 +8005,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" ht="16">
       <c r="A124">
         <v>138</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" ht="16">
       <c r="A125">
         <v>139</v>
       </c>
@@ -8045,7 +8045,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" ht="16">
       <c r="A126">
         <v>140</v>
       </c>
@@ -8065,7 +8065,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" ht="16">
       <c r="A127">
         <v>991</v>
       </c>
@@ -8085,7 +8085,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" ht="16">
       <c r="A128">
         <v>992</v>
       </c>
@@ -8105,7 +8105,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" ht="16">
       <c r="A129">
         <v>993</v>
       </c>
@@ -8125,7 +8125,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" ht="16">
       <c r="A130">
         <v>994</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="131" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" ht="16">
       <c r="A131">
         <v>995</v>
       </c>
@@ -8178,18 +8178,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P437"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="4"/>
-    <col min="2" max="2" width="53.1796875" customWidth="1"/>
-    <col min="11" max="11" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="63.453125" customWidth="1"/>
-    <col min="14" max="14" width="40.36328125" customWidth="1"/>
-    <col min="15" max="15" width="38.6328125" customWidth="1"/>
-    <col min="16" max="16" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5" style="4"/>
+    <col min="2" max="2" width="53.1640625" customWidth="1"/>
+    <col min="11" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="63.5" customWidth="1"/>
+    <col min="14" max="14" width="40.33203125" customWidth="1"/>
+    <col min="15" max="15" width="38.6640625" customWidth="1"/>
+    <col min="16" max="16" width="19.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -8239,7 +8239,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16">
       <c r="A2" s="4">
         <v>110</v>
       </c>
@@ -8283,7 +8283,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16">
       <c r="A3" s="4" t="s">
         <v>192</v>
       </c>
@@ -8312,7 +8312,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16">
       <c r="A4" s="4" t="s">
         <v>195</v>
       </c>
@@ -8356,7 +8356,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16">
       <c r="A5" s="4" t="s">
         <v>198</v>
       </c>
@@ -8385,7 +8385,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16">
       <c r="A6" s="4" t="s">
         <v>205</v>
       </c>
@@ -8429,7 +8429,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16">
       <c r="A7" s="4" t="s">
         <v>207</v>
       </c>
@@ -8473,7 +8473,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16">
       <c r="A8" s="4" t="s">
         <v>209</v>
       </c>
@@ -8517,7 +8517,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16">
       <c r="A9" s="4" t="s">
         <v>211</v>
       </c>
@@ -8546,7 +8546,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16">
       <c r="A10" s="4" t="s">
         <v>213</v>
       </c>
@@ -8584,7 +8584,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16">
       <c r="A11" s="4" t="s">
         <v>217</v>
       </c>
@@ -8628,7 +8628,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16">
       <c r="A12" s="4" t="s">
         <v>219</v>
       </c>
@@ -8657,7 +8657,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16">
       <c r="A13" s="4" t="s">
         <v>221</v>
       </c>
@@ -8686,7 +8686,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16">
       <c r="A14" s="4" t="s">
         <v>223</v>
       </c>
@@ -8715,7 +8715,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16">
       <c r="A15" s="4" t="s">
         <v>225</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16">
       <c r="A16" s="4" t="s">
         <v>227</v>
       </c>
@@ -8767,7 +8767,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16">
       <c r="A17" s="4" t="s">
         <v>229</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16">
       <c r="A18" s="4" t="s">
         <v>233</v>
       </c>
@@ -8813,7 +8813,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16">
       <c r="A19" s="4" t="s">
         <v>235</v>
       </c>
@@ -8842,7 +8842,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16">
       <c r="A20" s="4" t="s">
         <v>237</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16">
       <c r="A21" s="4" t="s">
         <v>239</v>
       </c>
@@ -8894,7 +8894,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16">
       <c r="A22" s="4" t="s">
         <v>241</v>
       </c>
@@ -8917,7 +8917,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16">
       <c r="A23" s="4" t="s">
         <v>243</v>
       </c>
@@ -8940,7 +8940,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16">
       <c r="A24" s="4" t="s">
         <v>245</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16">
       <c r="A25" s="4" t="s">
         <v>247</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16">
       <c r="A26" s="4" t="s">
         <v>249</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16">
       <c r="A27" s="4" t="s">
         <v>251</v>
       </c>
@@ -9038,7 +9038,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16">
       <c r="A28" s="4" t="s">
         <v>253</v>
       </c>
@@ -9067,7 +9067,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16">
       <c r="A29" s="4" t="s">
         <v>255</v>
       </c>
@@ -9111,7 +9111,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16">
       <c r="A30" s="4" t="s">
         <v>257</v>
       </c>
@@ -9134,7 +9134,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16">
       <c r="A31" s="4" t="s">
         <v>259</v>
       </c>
@@ -9163,7 +9163,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16">
       <c r="A32" s="4" t="s">
         <v>263</v>
       </c>
@@ -9192,7 +9192,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16">
       <c r="A33" s="4" t="s">
         <v>265</v>
       </c>
@@ -9221,7 +9221,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16">
       <c r="A34" s="4" t="s">
         <v>267</v>
       </c>
@@ -9244,7 +9244,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16">
       <c r="A35" s="4" t="s">
         <v>269</v>
       </c>
@@ -9273,7 +9273,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16">
       <c r="A36" s="4" t="s">
         <v>271</v>
       </c>
@@ -9296,7 +9296,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16">
       <c r="A37" s="4" t="s">
         <v>276</v>
       </c>
@@ -9319,7 +9319,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16">
       <c r="A38" s="4" t="s">
         <v>278</v>
       </c>
@@ -9342,7 +9342,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16">
       <c r="A39" s="4" t="s">
         <v>280</v>
       </c>
@@ -9365,7 +9365,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16">
       <c r="A40" s="4" t="s">
         <v>282</v>
       </c>
@@ -9394,7 +9394,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16">
       <c r="A41" s="4" t="s">
         <v>285</v>
       </c>
@@ -9417,7 +9417,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16">
       <c r="A42" s="4" t="s">
         <v>287</v>
       </c>
@@ -9461,7 +9461,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16">
       <c r="A43" s="4" t="s">
         <v>289</v>
       </c>
@@ -9490,7 +9490,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16">
       <c r="A44" s="4" t="s">
         <v>291</v>
       </c>
@@ -9513,7 +9513,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16">
       <c r="A45" s="4" t="s">
         <v>293</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16">
       <c r="A46" s="4" t="s">
         <v>295</v>
       </c>
@@ -9565,7 +9565,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16">
       <c r="A47" s="4" t="s">
         <v>297</v>
       </c>
@@ -9594,7 +9594,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16">
       <c r="A48" s="4" t="s">
         <v>299</v>
       </c>
@@ -9617,7 +9617,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16">
       <c r="A49" s="4" t="s">
         <v>301</v>
       </c>
@@ -9640,7 +9640,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16">
       <c r="A50" s="4" t="s">
         <v>303</v>
       </c>
@@ -9663,7 +9663,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16">
       <c r="A51" s="4" t="s">
         <v>305</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16">
       <c r="A52" s="4" t="s">
         <v>307</v>
       </c>
@@ -9715,7 +9715,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16">
       <c r="A53" s="4" t="s">
         <v>309</v>
       </c>
@@ -9747,7 +9747,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16">
       <c r="A54" s="4" t="s">
         <v>311</v>
       </c>
@@ -9770,7 +9770,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:16">
       <c r="A55" s="4" t="s">
         <v>313</v>
       </c>
@@ -9793,7 +9793,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:16">
       <c r="A56" s="4" t="s">
         <v>315</v>
       </c>
@@ -9822,7 +9822,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:16">
       <c r="A57" s="4" t="s">
         <v>317</v>
       </c>
@@ -9845,7 +9845,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:16">
       <c r="A58" s="4" t="s">
         <v>319</v>
       </c>
@@ -9868,7 +9868,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:16">
       <c r="A59" s="4" t="s">
         <v>321</v>
       </c>
@@ -9897,7 +9897,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:16">
       <c r="A60" s="4" t="s">
         <v>323</v>
       </c>
@@ -9941,7 +9941,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:16">
       <c r="A61" s="4" t="s">
         <v>327</v>
       </c>
@@ -9985,7 +9985,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:16">
       <c r="A62" s="4" t="s">
         <v>329</v>
       </c>
@@ -10017,7 +10017,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:16">
       <c r="A63" s="4" t="s">
         <v>331</v>
       </c>
@@ -10043,7 +10043,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:16">
       <c r="A64" s="4" t="s">
         <v>333</v>
       </c>
@@ -10078,7 +10078,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:16">
       <c r="A65" s="4" t="s">
         <v>335</v>
       </c>
@@ -10122,7 +10122,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:16">
       <c r="A66" s="4" t="s">
         <v>337</v>
       </c>
@@ -10151,7 +10151,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:16">
       <c r="A67" s="4" t="s">
         <v>339</v>
       </c>
@@ -10186,7 +10186,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:16">
       <c r="A68" s="4" t="s">
         <v>341</v>
       </c>
@@ -10215,7 +10215,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:16">
       <c r="A69" s="4" t="s">
         <v>343</v>
       </c>
@@ -10238,7 +10238,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:16">
       <c r="A70" s="4" t="s">
         <v>345</v>
       </c>
@@ -10261,7 +10261,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:16">
       <c r="A71" s="4" t="s">
         <v>347</v>
       </c>
@@ -10290,7 +10290,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:16">
       <c r="A72" s="4" t="s">
         <v>349</v>
       </c>
@@ -10313,7 +10313,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:16">
       <c r="A73" s="4" t="s">
         <v>351</v>
       </c>
@@ -10336,7 +10336,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:16">
       <c r="A74" s="4" t="s">
         <v>353</v>
       </c>
@@ -10365,7 +10365,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:16">
       <c r="A75" s="4" t="s">
         <v>355</v>
       </c>
@@ -10409,7 +10409,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:16">
       <c r="A76" s="4" t="s">
         <v>359</v>
       </c>
@@ -10447,7 +10447,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:16">
       <c r="A77" s="4" t="s">
         <v>361</v>
       </c>
@@ -10491,7 +10491,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:16">
       <c r="A78" s="4" t="s">
         <v>363</v>
       </c>
@@ -10529,7 +10529,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:16">
       <c r="A79" s="4" t="s">
         <v>365</v>
       </c>
@@ -10573,7 +10573,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:16">
       <c r="A80" s="4" t="s">
         <v>367</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:16">
       <c r="A81" s="4" t="s">
         <v>369</v>
       </c>
@@ -10643,7 +10643,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16">
       <c r="A82" s="4" t="s">
         <v>371</v>
       </c>
@@ -10675,7 +10675,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:16">
       <c r="A83" s="4" t="s">
         <v>373</v>
       </c>
@@ -10701,7 +10701,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:16">
       <c r="A84" s="4" t="s">
         <v>375</v>
       </c>
@@ -10736,7 +10736,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:16">
       <c r="A85" s="4" t="s">
         <v>377</v>
       </c>
@@ -10783,7 +10783,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16">
       <c r="A86" s="4" t="s">
         <v>379</v>
       </c>
@@ -10821,7 +10821,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16">
       <c r="A87" s="4" t="s">
         <v>381</v>
       </c>
@@ -10865,7 +10865,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:16">
       <c r="A88" s="4" t="s">
         <v>385</v>
       </c>
@@ -10894,7 +10894,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:16">
       <c r="A89" s="4" t="s">
         <v>387</v>
       </c>
@@ -10917,7 +10917,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16">
       <c r="A90" s="4" t="s">
         <v>389</v>
       </c>
@@ -10961,7 +10961,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16">
       <c r="A91" s="4" t="s">
         <v>391</v>
       </c>
@@ -10990,7 +10990,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16">
       <c r="A92" s="4" t="s">
         <v>393</v>
       </c>
@@ -11019,7 +11019,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:16">
       <c r="A93" s="4" t="s">
         <v>395</v>
       </c>
@@ -11063,7 +11063,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16">
       <c r="A94" s="4" t="s">
         <v>397</v>
       </c>
@@ -11092,7 +11092,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16">
       <c r="A95" s="4" t="s">
         <v>399</v>
       </c>
@@ -11130,7 +11130,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16">
       <c r="A96" s="4" t="s">
         <v>401</v>
       </c>
@@ -11159,7 +11159,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:16">
       <c r="A97" s="4" t="s">
         <v>403</v>
       </c>
@@ -11188,7 +11188,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:16">
       <c r="A98" s="4" t="s">
         <v>405</v>
       </c>
@@ -11211,7 +11211,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:16">
       <c r="A99" s="4" t="s">
         <v>409</v>
       </c>
@@ -11234,7 +11234,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:16">
       <c r="A100" s="4" t="s">
         <v>411</v>
       </c>
@@ -11257,7 +11257,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:16">
       <c r="A101" s="4" t="s">
         <v>413</v>
       </c>
@@ -11286,7 +11286,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:16">
       <c r="A102" s="4" t="s">
         <v>415</v>
       </c>
@@ -11309,7 +11309,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:16">
       <c r="A103" s="4" t="s">
         <v>417</v>
       </c>
@@ -11332,7 +11332,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:16">
       <c r="A104" s="4" t="s">
         <v>419</v>
       </c>
@@ -11355,7 +11355,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:16">
       <c r="A105" s="4" t="s">
         <v>421</v>
       </c>
@@ -11384,7 +11384,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:16">
       <c r="A106" s="4" t="s">
         <v>423</v>
       </c>
@@ -11407,7 +11407,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:16">
       <c r="A107" s="4" t="s">
         <v>425</v>
       </c>
@@ -11451,7 +11451,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:16">
       <c r="A108" s="4" t="s">
         <v>429</v>
       </c>
@@ -11474,7 +11474,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:16">
       <c r="A109" s="4" t="s">
         <v>431</v>
       </c>
@@ -11497,7 +11497,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:16">
       <c r="A110" s="4" t="s">
         <v>433</v>
       </c>
@@ -11520,7 +11520,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:16">
       <c r="A111" s="4" t="s">
         <v>435</v>
       </c>
@@ -11543,7 +11543,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:16">
       <c r="A112" s="4" t="s">
         <v>437</v>
       </c>
@@ -11566,7 +11566,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:16">
       <c r="A113" s="4" t="s">
         <v>439</v>
       </c>
@@ -11589,7 +11589,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:16">
       <c r="A114" s="4" t="s">
         <v>441</v>
       </c>
@@ -11612,7 +11612,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:16">
       <c r="A115" s="4" t="s">
         <v>443</v>
       </c>
@@ -11635,7 +11635,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:16">
       <c r="A116" s="4" t="s">
         <v>445</v>
       </c>
@@ -11664,7 +11664,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:16">
       <c r="A117" s="4" t="s">
         <v>447</v>
       </c>
@@ -11693,7 +11693,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:16">
       <c r="A118" s="4" t="s">
         <v>449</v>
       </c>
@@ -11716,7 +11716,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:16">
       <c r="A119" s="4" t="s">
         <v>451</v>
       </c>
@@ -11745,7 +11745,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:16">
       <c r="A120" s="4" t="s">
         <v>453</v>
       </c>
@@ -11768,7 +11768,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:16">
       <c r="A121" s="4" t="s">
         <v>455</v>
       </c>
@@ -11791,7 +11791,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:16">
       <c r="A122" s="4" t="s">
         <v>457</v>
       </c>
@@ -11820,7 +11820,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:16">
       <c r="A123" s="4" t="s">
         <v>459</v>
       </c>
@@ -11849,7 +11849,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:16">
       <c r="A124" s="4" t="s">
         <v>461</v>
       </c>
@@ -11872,7 +11872,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:16">
       <c r="A125" s="4" t="s">
         <v>463</v>
       </c>
@@ -11895,7 +11895,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:16">
       <c r="A126" s="4" t="s">
         <v>465</v>
       </c>
@@ -11930,7 +11930,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:16">
       <c r="A127" s="4" t="s">
         <v>467</v>
       </c>
@@ -11959,7 +11959,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:16">
       <c r="A128" s="4" t="s">
         <v>469</v>
       </c>
@@ -11988,7 +11988,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:16">
       <c r="A129" s="4" t="s">
         <v>475</v>
       </c>
@@ -12032,7 +12032,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:16">
       <c r="A130" s="4" t="s">
         <v>477</v>
       </c>
@@ -12061,7 +12061,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:16">
       <c r="A131" s="4" t="s">
         <v>479</v>
       </c>
@@ -12084,7 +12084,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:16">
       <c r="A132" s="4" t="s">
         <v>481</v>
       </c>
@@ -12116,7 +12116,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:16">
       <c r="A133" s="4" t="s">
         <v>483</v>
       </c>
@@ -12145,7 +12145,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:16">
       <c r="A134" s="4" t="s">
         <v>485</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:16">
       <c r="A135" s="4" t="s">
         <v>487</v>
       </c>
@@ -12197,7 +12197,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:16">
       <c r="A136" s="4" t="s">
         <v>489</v>
       </c>
@@ -12226,7 +12226,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:16">
       <c r="A137" s="4" t="s">
         <v>491</v>
       </c>
@@ -12249,7 +12249,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:16">
       <c r="A138" s="4" t="s">
         <v>493</v>
       </c>
@@ -12278,7 +12278,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:16">
       <c r="A139" s="4" t="s">
         <v>495</v>
       </c>
@@ -12307,7 +12307,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:16">
       <c r="A140" s="4" t="s">
         <v>497</v>
       </c>
@@ -12336,7 +12336,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:16">
       <c r="A141" s="4" t="s">
         <v>499</v>
       </c>
@@ -12359,7 +12359,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:16">
       <c r="A142" s="4" t="s">
         <v>501</v>
       </c>
@@ -12382,7 +12382,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:16">
       <c r="A143" s="4" t="s">
         <v>503</v>
       </c>
@@ -12411,7 +12411,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:16">
       <c r="A144" s="4" t="s">
         <v>505</v>
       </c>
@@ -12434,7 +12434,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:16">
       <c r="A145" s="4" t="s">
         <v>507</v>
       </c>
@@ -12457,7 +12457,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:16">
       <c r="A146" s="4" t="s">
         <v>509</v>
       </c>
@@ -12489,7 +12489,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:16">
       <c r="A147" s="4" t="s">
         <v>511</v>
       </c>
@@ -12527,7 +12527,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:16">
       <c r="A148" s="4" t="s">
         <v>513</v>
       </c>
@@ -12571,7 +12571,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:16">
       <c r="A149" s="4" t="s">
         <v>515</v>
       </c>
@@ -12594,7 +12594,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:16">
       <c r="A150" s="4" t="s">
         <v>517</v>
       </c>
@@ -12617,7 +12617,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:16">
       <c r="A151" s="4" t="s">
         <v>519</v>
       </c>
@@ -12646,7 +12646,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:16">
       <c r="A152" s="4" t="s">
         <v>521</v>
       </c>
@@ -12675,7 +12675,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:16">
       <c r="A153" s="4" t="s">
         <v>523</v>
       </c>
@@ -12698,7 +12698,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:16">
       <c r="A154" s="4" t="s">
         <v>525</v>
       </c>
@@ -12736,7 +12736,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:16">
       <c r="A155" s="4" t="s">
         <v>529</v>
       </c>
@@ -12780,7 +12780,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:16">
       <c r="A156" s="4" t="s">
         <v>531</v>
       </c>
@@ -12824,7 +12824,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:16">
       <c r="A157" s="4" t="s">
         <v>533</v>
       </c>
@@ -12853,7 +12853,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:16">
       <c r="A158" s="4" t="s">
         <v>535</v>
       </c>
@@ -12897,7 +12897,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:16">
       <c r="A159" s="4" t="s">
         <v>537</v>
       </c>
@@ -12929,7 +12929,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:16">
       <c r="A160" s="4" t="s">
         <v>539</v>
       </c>
@@ -12952,7 +12952,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:16">
       <c r="A161" s="4" t="s">
         <v>541</v>
       </c>
@@ -12996,7 +12996,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:16">
       <c r="A162" s="4" t="s">
         <v>543</v>
       </c>
@@ -13019,7 +13019,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:16">
       <c r="A163" s="4" t="s">
         <v>545</v>
       </c>
@@ -13048,7 +13048,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:16">
       <c r="A164" s="4" t="s">
         <v>547</v>
       </c>
@@ -13086,7 +13086,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:16">
       <c r="A165" s="4" t="s">
         <v>549</v>
       </c>
@@ -13109,7 +13109,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:16">
       <c r="A166" s="4" t="s">
         <v>551</v>
       </c>
@@ -13132,7 +13132,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:16">
       <c r="A167" s="4" t="s">
         <v>553</v>
       </c>
@@ -13170,7 +13170,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:16">
       <c r="A168" s="4" t="s">
         <v>555</v>
       </c>
@@ -13199,7 +13199,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:16">
       <c r="A169" s="4" t="s">
         <v>557</v>
       </c>
@@ -13222,7 +13222,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:16">
       <c r="A170" s="4" t="s">
         <v>559</v>
       </c>
@@ -13251,7 +13251,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:16">
       <c r="A171" s="4" t="s">
         <v>561</v>
       </c>
@@ -13280,7 +13280,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:16">
       <c r="A172" s="4" t="s">
         <v>565</v>
       </c>
@@ -13324,7 +13324,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:16">
       <c r="A173" s="4" t="s">
         <v>567</v>
       </c>
@@ -13368,7 +13368,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:16">
       <c r="A174" s="4" t="s">
         <v>569</v>
       </c>
@@ -13397,7 +13397,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:16">
       <c r="A175" s="4" t="s">
         <v>571</v>
       </c>
@@ -13426,7 +13426,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:16">
       <c r="A176" s="4" t="s">
         <v>573</v>
       </c>
@@ -13455,7 +13455,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:16">
       <c r="A177" s="4" t="s">
         <v>575</v>
       </c>
@@ -13499,7 +13499,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:16">
       <c r="A178" s="4" t="s">
         <v>577</v>
       </c>
@@ -13522,7 +13522,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:16">
       <c r="A179" s="4" t="s">
         <v>579</v>
       </c>
@@ -13551,7 +13551,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:16">
       <c r="A180" s="4" t="s">
         <v>581</v>
       </c>
@@ -13580,7 +13580,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:16">
       <c r="A181" s="4" t="s">
         <v>583</v>
       </c>
@@ -13609,7 +13609,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:16">
       <c r="A182" s="4" t="s">
         <v>585</v>
       </c>
@@ -13644,7 +13644,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:16">
       <c r="A183" s="4" t="s">
         <v>587</v>
       </c>
@@ -13673,7 +13673,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:16">
       <c r="A184" s="4" t="s">
         <v>589</v>
       </c>
@@ -13702,7 +13702,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:16">
       <c r="A185" s="4" t="s">
         <v>591</v>
       </c>
@@ -13746,7 +13746,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:16">
       <c r="A186" s="4" t="s">
         <v>593</v>
       </c>
@@ -13769,7 +13769,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:16">
       <c r="A187" s="4" t="s">
         <v>595</v>
       </c>
@@ -13813,7 +13813,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:16">
       <c r="A188" s="4" t="s">
         <v>597</v>
       </c>
@@ -13842,7 +13842,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:16">
       <c r="A189" s="4" t="s">
         <v>599</v>
       </c>
@@ -13865,7 +13865,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:16">
       <c r="A190" s="4" t="s">
         <v>601</v>
       </c>
@@ -13894,7 +13894,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:16">
       <c r="A191" s="4" t="s">
         <v>603</v>
       </c>
@@ -13938,7 +13938,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:16">
       <c r="A192" s="4" t="s">
         <v>605</v>
       </c>
@@ -13967,7 +13967,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:16">
       <c r="A193" s="4" t="s">
         <v>607</v>
       </c>
@@ -14011,7 +14011,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:16">
       <c r="A194" s="4" t="s">
         <v>609</v>
       </c>
@@ -14040,7 +14040,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:16">
       <c r="A195" s="4" t="s">
         <v>611</v>
       </c>
@@ -14072,7 +14072,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:16">
       <c r="A196" s="4" t="s">
         <v>615</v>
       </c>
@@ -14110,7 +14110,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:16">
       <c r="A197" s="4" t="s">
         <v>617</v>
       </c>
@@ -14139,7 +14139,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:16">
       <c r="A198" s="4" t="s">
         <v>619</v>
       </c>
@@ -14168,7 +14168,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:16">
       <c r="A199" s="4" t="s">
         <v>621</v>
       </c>
@@ -14197,7 +14197,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:16">
       <c r="A200" s="4" t="s">
         <v>623</v>
       </c>
@@ -14220,7 +14220,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:16">
       <c r="A201" s="4" t="s">
         <v>625</v>
       </c>
@@ -14243,7 +14243,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:16">
       <c r="A202" s="4" t="s">
         <v>627</v>
       </c>
@@ -14266,7 +14266,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:16">
       <c r="A203" s="4" t="s">
         <v>629</v>
       </c>
@@ -14289,7 +14289,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:16">
       <c r="A204" s="4" t="s">
         <v>631</v>
       </c>
@@ -14318,7 +14318,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:16">
       <c r="A205" s="4" t="s">
         <v>633</v>
       </c>
@@ -14347,7 +14347,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:16">
       <c r="A206" s="4" t="s">
         <v>635</v>
       </c>
@@ -14385,7 +14385,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:16">
       <c r="A207" s="4" t="s">
         <v>639</v>
       </c>
@@ -14420,7 +14420,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:16">
       <c r="A208" s="4" t="s">
         <v>641</v>
       </c>
@@ -14449,7 +14449,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:16">
       <c r="A209" s="4" t="s">
         <v>643</v>
       </c>
@@ -14472,7 +14472,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:16">
       <c r="A210" s="4" t="s">
         <v>645</v>
       </c>
@@ -14516,7 +14516,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:16">
       <c r="A211" s="4" t="s">
         <v>647</v>
       </c>
@@ -14560,7 +14560,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:16">
       <c r="A212" s="4" t="s">
         <v>649</v>
       </c>
@@ -14604,7 +14604,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:16">
       <c r="A213" s="4" t="s">
         <v>656</v>
       </c>
@@ -14648,7 +14648,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:16">
       <c r="A214" s="4" t="s">
         <v>658</v>
       </c>
@@ -14686,7 +14686,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:16">
       <c r="A215" s="4" t="s">
         <v>660</v>
       </c>
@@ -14730,7 +14730,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:16">
       <c r="A216" s="4" t="s">
         <v>662</v>
       </c>
@@ -14768,7 +14768,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:16">
       <c r="A217" s="4" t="s">
         <v>666</v>
       </c>
@@ -14797,7 +14797,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:16">
       <c r="A218" s="4" t="s">
         <v>668</v>
       </c>
@@ -14820,7 +14820,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:16">
       <c r="A219" s="4" t="s">
         <v>670</v>
       </c>
@@ -14861,7 +14861,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:16">
       <c r="A220" s="4" t="s">
         <v>672</v>
       </c>
@@ -14890,7 +14890,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:16">
       <c r="A221" s="4" t="s">
         <v>674</v>
       </c>
@@ -14919,7 +14919,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:16">
       <c r="A222" s="4" t="s">
         <v>676</v>
       </c>
@@ -14948,7 +14948,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:16">
       <c r="A223" s="4" t="s">
         <v>678</v>
       </c>
@@ -14980,7 +14980,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:16">
       <c r="A224" s="4" t="s">
         <v>680</v>
       </c>
@@ -15015,7 +15015,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:16">
       <c r="A225" s="4" t="s">
         <v>682</v>
       </c>
@@ -15056,7 +15056,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:16">
       <c r="A226" s="4" t="s">
         <v>684</v>
       </c>
@@ -15094,7 +15094,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:16">
       <c r="A227" s="4" t="s">
         <v>686</v>
       </c>
@@ -15132,7 +15132,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:16">
       <c r="A228" s="4" t="s">
         <v>688</v>
       </c>
@@ -15170,7 +15170,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:16">
       <c r="A229" s="4" t="s">
         <v>692</v>
       </c>
@@ -15214,7 +15214,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:16">
       <c r="A230" s="4" t="s">
         <v>694</v>
       </c>
@@ -15243,7 +15243,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:16">
       <c r="A231" s="4" t="s">
         <v>696</v>
       </c>
@@ -15272,7 +15272,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:16">
       <c r="A232" s="4" t="s">
         <v>698</v>
       </c>
@@ -15304,7 +15304,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:16">
       <c r="A233" s="4" t="s">
         <v>700</v>
       </c>
@@ -15327,7 +15327,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:16">
       <c r="A234" s="4" t="s">
         <v>702</v>
       </c>
@@ -15356,7 +15356,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:16">
       <c r="A235" s="4" t="s">
         <v>706</v>
       </c>
@@ -15400,7 +15400,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:16">
       <c r="A236" s="4" t="s">
         <v>708</v>
       </c>
@@ -15429,7 +15429,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:16">
       <c r="A237" s="4" t="s">
         <v>710</v>
       </c>
@@ -15473,7 +15473,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:16">
       <c r="A238" s="4" t="s">
         <v>712</v>
       </c>
@@ -15508,7 +15508,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:16">
       <c r="A239" s="4" t="s">
         <v>714</v>
       </c>
@@ -15552,7 +15552,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:16">
       <c r="A240" s="4" t="s">
         <v>716</v>
       </c>
@@ -15596,7 +15596,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:16">
       <c r="A241" s="4" t="s">
         <v>718</v>
       </c>
@@ -15640,7 +15640,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:16">
       <c r="A242" s="4" t="s">
         <v>724</v>
       </c>
@@ -15669,7 +15669,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:16">
       <c r="A243" s="4" t="s">
         <v>726</v>
       </c>
@@ -15698,7 +15698,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:16">
       <c r="A244" s="4" t="s">
         <v>728</v>
       </c>
@@ -15742,7 +15742,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:16">
       <c r="A245" s="4" t="s">
         <v>730</v>
       </c>
@@ -15786,7 +15786,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:16">
       <c r="A246" s="4" t="s">
         <v>732</v>
       </c>
@@ -15815,7 +15815,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:16">
       <c r="A247" s="4" t="s">
         <v>734</v>
       </c>
@@ -15859,7 +15859,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:16">
       <c r="A248" s="4" t="s">
         <v>736</v>
       </c>
@@ -15888,7 +15888,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:16">
       <c r="A249" s="4" t="s">
         <v>738</v>
       </c>
@@ -15926,7 +15926,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:16">
       <c r="A250" s="4" t="s">
         <v>740</v>
       </c>
@@ -15958,7 +15958,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:16">
       <c r="A251" s="4" t="s">
         <v>742</v>
       </c>
@@ -16002,7 +16002,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:16">
       <c r="A252" s="4" t="s">
         <v>744</v>
       </c>
@@ -16031,7 +16031,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:16">
       <c r="A253" s="4" t="s">
         <v>746</v>
       </c>
@@ -16054,7 +16054,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:16">
       <c r="A254" s="4" t="s">
         <v>748</v>
       </c>
@@ -16083,7 +16083,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:16">
       <c r="A255" s="4" t="s">
         <v>750</v>
       </c>
@@ -16106,7 +16106,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:16">
       <c r="A256" s="4" t="s">
         <v>752</v>
       </c>
@@ -16135,7 +16135,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:16">
       <c r="A257" s="4" t="s">
         <v>754</v>
       </c>
@@ -16170,7 +16170,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:16">
       <c r="A258" s="4" t="s">
         <v>756</v>
       </c>
@@ -16208,7 +16208,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:16">
       <c r="A259" s="4" t="s">
         <v>760</v>
       </c>
@@ -16246,7 +16246,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:16">
       <c r="A260" s="4" t="s">
         <v>762</v>
       </c>
@@ -16290,7 +16290,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:16">
       <c r="A261" s="4" t="s">
         <v>764</v>
       </c>
@@ -16334,7 +16334,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:16">
       <c r="A262" s="4" t="s">
         <v>766</v>
       </c>
@@ -16378,7 +16378,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:16">
       <c r="A263" s="4" t="s">
         <v>768</v>
       </c>
@@ -16422,7 +16422,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:16">
       <c r="A264" s="4" t="s">
         <v>770</v>
       </c>
@@ -16445,7 +16445,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:16">
       <c r="A265" s="4" t="s">
         <v>772</v>
       </c>
@@ -16489,7 +16489,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:16">
       <c r="A266" s="4" t="s">
         <v>774</v>
       </c>
@@ -16533,7 +16533,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:16">
       <c r="A267" s="4" t="s">
         <v>776</v>
       </c>
@@ -16562,7 +16562,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:16">
       <c r="A268" s="4" t="s">
         <v>778</v>
       </c>
@@ -16600,7 +16600,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:16">
       <c r="A269" s="4" t="s">
         <v>780</v>
       </c>
@@ -16632,7 +16632,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:16">
       <c r="A270" s="4" t="s">
         <v>782</v>
       </c>
@@ -16661,7 +16661,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:16">
       <c r="A271" s="4" t="s">
         <v>784</v>
       </c>
@@ -16690,7 +16690,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:16">
       <c r="A272" s="4" t="s">
         <v>788</v>
       </c>
@@ -16725,7 +16725,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:16">
       <c r="A273" s="4" t="s">
         <v>790</v>
       </c>
@@ -16766,7 +16766,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:16">
       <c r="A274" s="4" t="s">
         <v>792</v>
       </c>
@@ -16795,7 +16795,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:16">
       <c r="A275" s="4" t="s">
         <v>794</v>
       </c>
@@ -16824,7 +16824,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:16">
       <c r="A276" s="4" t="s">
         <v>796</v>
       </c>
@@ -16847,7 +16847,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:16">
       <c r="A277" s="4" t="s">
         <v>800</v>
       </c>
@@ -16891,7 +16891,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:16">
       <c r="A278" s="4" t="s">
         <v>802</v>
       </c>
@@ -16914,7 +16914,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:16">
       <c r="A279" s="4" t="s">
         <v>804</v>
       </c>
@@ -16958,7 +16958,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:16">
       <c r="A280" s="4" t="s">
         <v>806</v>
       </c>
@@ -17002,7 +17002,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:16">
       <c r="A281" s="4" t="s">
         <v>808</v>
       </c>
@@ -17037,7 +17037,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:16">
       <c r="A282" s="4" t="s">
         <v>814</v>
       </c>
@@ -17075,7 +17075,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:16">
       <c r="A283" s="4" t="s">
         <v>816</v>
       </c>
@@ -17119,7 +17119,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:16">
       <c r="A284" s="4" t="s">
         <v>818</v>
       </c>
@@ -17157,7 +17157,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:16">
       <c r="A285" s="4" t="s">
         <v>820</v>
       </c>
@@ -17186,7 +17186,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:16">
       <c r="A286" s="4" t="s">
         <v>822</v>
       </c>
@@ -17224,7 +17224,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:16">
       <c r="A287" s="4" t="s">
         <v>824</v>
       </c>
@@ -17247,7 +17247,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:16">
       <c r="A288" s="4" t="s">
         <v>826</v>
       </c>
@@ -17270,7 +17270,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:16">
       <c r="A289" s="4" t="s">
         <v>828</v>
       </c>
@@ -17305,7 +17305,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:16">
       <c r="A290" s="4" t="s">
         <v>830</v>
       </c>
@@ -17337,7 +17337,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:16">
       <c r="A291" s="4" t="s">
         <v>834</v>
       </c>
@@ -17360,7 +17360,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:16">
       <c r="A292" s="4" t="s">
         <v>836</v>
       </c>
@@ -17383,7 +17383,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:16">
       <c r="A293" s="4" t="s">
         <v>838</v>
       </c>
@@ -17406,7 +17406,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:16">
       <c r="A294" s="4" t="s">
         <v>840</v>
       </c>
@@ -17429,7 +17429,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:16">
       <c r="A295" s="4" t="s">
         <v>842</v>
       </c>
@@ -17464,7 +17464,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:16">
       <c r="A296" s="4" t="s">
         <v>846</v>
       </c>
@@ -17487,7 +17487,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:16">
       <c r="A297" s="4" t="s">
         <v>848</v>
       </c>
@@ -17528,7 +17528,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:16">
       <c r="A298" s="4" t="s">
         <v>850</v>
       </c>
@@ -17557,7 +17557,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:16">
       <c r="A299" s="4" t="s">
         <v>852</v>
       </c>
@@ -17601,7 +17601,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:16">
       <c r="A300" s="4" t="s">
         <v>858</v>
       </c>
@@ -17645,7 +17645,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:16">
       <c r="A301" s="4" t="s">
         <v>860</v>
       </c>
@@ -17689,7 +17689,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:16">
       <c r="A302" s="4" t="s">
         <v>862</v>
       </c>
@@ -17733,7 +17733,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:16">
       <c r="A303" s="4" t="s">
         <v>864</v>
       </c>
@@ -17777,7 +17777,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:16">
       <c r="A304" s="4" t="s">
         <v>866</v>
       </c>
@@ -17806,7 +17806,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:16">
       <c r="A305" s="4" t="s">
         <v>868</v>
       </c>
@@ -17850,7 +17850,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:16">
       <c r="A306" s="4" t="s">
         <v>870</v>
       </c>
@@ -17879,7 +17879,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:16">
       <c r="A307" s="4" t="s">
         <v>872</v>
       </c>
@@ -17908,7 +17908,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:16">
       <c r="A308" s="4" t="s">
         <v>874</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:16">
       <c r="A309" s="4" t="s">
         <v>876</v>
       </c>
@@ -17960,7 +17960,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:16">
       <c r="A310" s="4" t="s">
         <v>878</v>
       </c>
@@ -17989,7 +17989,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:16">
       <c r="A311" s="4" t="s">
         <v>880</v>
       </c>
@@ -18012,7 +18012,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:16">
       <c r="A312" s="4" t="s">
         <v>882</v>
       </c>
@@ -18056,7 +18056,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:16">
       <c r="A313" s="4" t="s">
         <v>884</v>
       </c>
@@ -18100,7 +18100,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:16">
       <c r="A314" s="4" t="s">
         <v>886</v>
       </c>
@@ -18123,7 +18123,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="315" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:16">
       <c r="A315" s="4" t="s">
         <v>888</v>
       </c>
@@ -18152,7 +18152,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:16">
       <c r="A316" s="4" t="s">
         <v>892</v>
       </c>
@@ -18181,7 +18181,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:16">
       <c r="A317" s="4" t="s">
         <v>894</v>
       </c>
@@ -18210,7 +18210,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:16">
       <c r="A318" s="4" t="s">
         <v>896</v>
       </c>
@@ -18239,7 +18239,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:16">
       <c r="A319" s="4" t="s">
         <v>898</v>
       </c>
@@ -18268,7 +18268,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:16">
       <c r="A320" s="4" t="s">
         <v>900</v>
       </c>
@@ -18297,7 +18297,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:16">
       <c r="A321" s="4" t="s">
         <v>902</v>
       </c>
@@ -18326,7 +18326,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="322" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:16">
       <c r="A322" s="4" t="s">
         <v>904</v>
       </c>
@@ -18355,7 +18355,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="323" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:16">
       <c r="A323" s="4" t="s">
         <v>906</v>
       </c>
@@ -18384,7 +18384,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="324" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:16">
       <c r="A324" s="4" t="s">
         <v>908</v>
       </c>
@@ -18413,7 +18413,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="325" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:16">
       <c r="A325" s="4" t="s">
         <v>910</v>
       </c>
@@ -18436,7 +18436,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="326" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:16">
       <c r="A326" s="4" t="s">
         <v>912</v>
       </c>
@@ -18465,7 +18465,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:16">
       <c r="A327" s="4" t="s">
         <v>914</v>
       </c>
@@ -18494,7 +18494,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:16">
       <c r="A328" s="4" t="s">
         <v>916</v>
       </c>
@@ -18523,7 +18523,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:16">
       <c r="A329" s="4" t="s">
         <v>920</v>
       </c>
@@ -18552,7 +18552,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:16">
       <c r="A330" s="4" t="s">
         <v>922</v>
       </c>
@@ -18581,7 +18581,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:16">
       <c r="A331" s="4" t="s">
         <v>924</v>
       </c>
@@ -18610,7 +18610,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:16">
       <c r="A332" s="4" t="s">
         <v>926</v>
       </c>
@@ -18639,7 +18639,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:16">
       <c r="A333" s="4" t="s">
         <v>928</v>
       </c>
@@ -18668,7 +18668,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:16">
       <c r="A334" s="4" t="s">
         <v>930</v>
       </c>
@@ -18697,7 +18697,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="335" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:16">
       <c r="A335" s="4" t="s">
         <v>932</v>
       </c>
@@ -18738,7 +18738,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="336" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:16">
       <c r="A336" s="4" t="s">
         <v>934</v>
       </c>
@@ -18770,7 +18770,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="337" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:16">
       <c r="A337" s="4" t="s">
         <v>936</v>
       </c>
@@ -18799,7 +18799,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="338" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:16">
       <c r="A338" s="4" t="s">
         <v>938</v>
       </c>
@@ -18828,7 +18828,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="339" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:16">
       <c r="A339" s="4" t="s">
         <v>940</v>
       </c>
@@ -18857,7 +18857,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="340" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:16">
       <c r="A340" s="4" t="s">
         <v>942</v>
       </c>
@@ -18886,7 +18886,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:16">
       <c r="A341" s="4" t="s">
         <v>946</v>
       </c>
@@ -18915,7 +18915,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="342" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:16">
       <c r="A342" s="4" t="s">
         <v>948</v>
       </c>
@@ -18944,7 +18944,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="343" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:16">
       <c r="A343" s="4" t="s">
         <v>950</v>
       </c>
@@ -18973,7 +18973,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="344" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:16">
       <c r="A344" s="4" t="s">
         <v>952</v>
       </c>
@@ -19002,7 +19002,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="345" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:16">
       <c r="A345" s="4" t="s">
         <v>954</v>
       </c>
@@ -19031,7 +19031,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="346" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:16">
       <c r="A346" s="4" t="s">
         <v>958</v>
       </c>
@@ -19075,7 +19075,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="347" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:16">
       <c r="A347" s="4" t="s">
         <v>960</v>
       </c>
@@ -19098,7 +19098,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="348" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:16">
       <c r="A348" s="4" t="s">
         <v>962</v>
       </c>
@@ -19130,7 +19130,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="349" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:16">
       <c r="A349" s="4" t="s">
         <v>964</v>
       </c>
@@ -19162,7 +19162,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="350" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:16">
       <c r="A350" s="4" t="s">
         <v>966</v>
       </c>
@@ -19185,7 +19185,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:16">
       <c r="A351" s="4" t="s">
         <v>968</v>
       </c>
@@ -19214,7 +19214,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:16">
       <c r="A352" s="4" t="s">
         <v>970</v>
       </c>
@@ -19258,7 +19258,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:16">
       <c r="A353" s="4" t="s">
         <v>972</v>
       </c>
@@ -19287,7 +19287,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:16">
       <c r="A354" s="4" t="s">
         <v>974</v>
       </c>
@@ -19325,7 +19325,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:16">
       <c r="A355" s="4" t="s">
         <v>976</v>
       </c>
@@ -19363,7 +19363,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="356" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:16">
       <c r="A356" s="4" t="s">
         <v>978</v>
       </c>
@@ -19398,7 +19398,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:16">
       <c r="A357" s="4" t="s">
         <v>980</v>
       </c>
@@ -19430,7 +19430,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:16">
       <c r="A358" s="4" t="s">
         <v>982</v>
       </c>
@@ -19453,7 +19453,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="359" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:16">
       <c r="A359" s="4" t="s">
         <v>984</v>
       </c>
@@ -19482,7 +19482,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:16">
       <c r="A360" s="4" t="s">
         <v>986</v>
       </c>
@@ -19511,7 +19511,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:16">
       <c r="A361" s="4" t="s">
         <v>988</v>
       </c>
@@ -19540,7 +19540,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:16">
       <c r="A362" s="4" t="s">
         <v>990</v>
       </c>
@@ -19569,7 +19569,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:16">
       <c r="A363" s="4" t="s">
         <v>992</v>
       </c>
@@ -19598,7 +19598,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:16">
       <c r="A364" s="4" t="s">
         <v>994</v>
       </c>
@@ -19642,7 +19642,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:16">
       <c r="A365" s="4" t="s">
         <v>996</v>
       </c>
@@ -19680,7 +19680,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:16">
       <c r="A366" s="4" t="s">
         <v>1001</v>
       </c>
@@ -19724,7 +19724,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:16">
       <c r="A367" s="4" t="s">
         <v>1003</v>
       </c>
@@ -19753,7 +19753,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:16">
       <c r="A368" s="4" t="s">
         <v>1005</v>
       </c>
@@ -19782,7 +19782,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:16">
       <c r="A369" s="4" t="s">
         <v>1007</v>
       </c>
@@ -19811,7 +19811,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:16">
       <c r="A370" s="4" t="s">
         <v>1009</v>
       </c>
@@ -19840,7 +19840,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="371" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:16">
       <c r="A371" s="4" t="s">
         <v>1011</v>
       </c>
@@ -19869,7 +19869,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:16">
       <c r="A372" s="4" t="s">
         <v>1013</v>
       </c>
@@ -19892,7 +19892,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="373" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:16">
       <c r="A373" s="4" t="s">
         <v>1015</v>
       </c>
@@ -19921,7 +19921,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:16">
       <c r="A374" s="4" t="s">
         <v>1017</v>
       </c>
@@ -19950,7 +19950,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="375" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:16">
       <c r="A375" s="4" t="s">
         <v>1019</v>
       </c>
@@ -19979,7 +19979,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:16">
       <c r="A376" s="4" t="s">
         <v>1021</v>
       </c>
@@ -20008,7 +20008,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="377" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:16">
       <c r="A377" s="4" t="s">
         <v>1023</v>
       </c>
@@ -20037,7 +20037,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:16">
       <c r="A378" s="4" t="s">
         <v>1025</v>
       </c>
@@ -20069,7 +20069,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:16">
       <c r="A379" s="4" t="s">
         <v>1027</v>
       </c>
@@ -20098,7 +20098,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:16">
       <c r="A380" s="4" t="s">
         <v>1029</v>
       </c>
@@ -20121,7 +20121,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:16">
       <c r="A381" s="4" t="s">
         <v>1031</v>
       </c>
@@ -20150,7 +20150,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:16">
       <c r="A382" s="4" t="s">
         <v>1033</v>
       </c>
@@ -20173,7 +20173,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:16">
       <c r="A383" s="4" t="s">
         <v>1035</v>
       </c>
@@ -20202,7 +20202,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:16">
       <c r="A384" s="4" t="s">
         <v>1037</v>
       </c>
@@ -20231,7 +20231,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="385" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:16">
       <c r="A385" s="4" t="s">
         <v>1039</v>
       </c>
@@ -20260,7 +20260,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:16">
       <c r="A386" s="4" t="s">
         <v>1041</v>
       </c>
@@ -20289,7 +20289,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="387" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:16">
       <c r="A387" s="4" t="s">
         <v>1043</v>
       </c>
@@ -20318,7 +20318,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="388" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:16">
       <c r="A388" s="4" t="s">
         <v>1045</v>
       </c>
@@ -20341,7 +20341,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="389" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:16">
       <c r="A389" s="4" t="s">
         <v>1047</v>
       </c>
@@ -20385,7 +20385,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="390" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:16">
       <c r="A390" s="4" t="s">
         <v>1049</v>
       </c>
@@ -20414,7 +20414,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="391" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:16">
       <c r="A391" s="4" t="s">
         <v>1051</v>
       </c>
@@ -20443,7 +20443,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="392" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:16">
       <c r="A392" s="4" t="s">
         <v>1055</v>
       </c>
@@ -20472,7 +20472,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="393" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:16">
       <c r="A393" s="4" t="s">
         <v>1057</v>
       </c>
@@ -20501,7 +20501,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="394" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:16">
       <c r="A394" s="4" t="s">
         <v>1059</v>
       </c>
@@ -20524,7 +20524,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:16">
       <c r="A395" s="4" t="s">
         <v>1063</v>
       </c>
@@ -20547,7 +20547,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="396" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:16">
       <c r="A396" s="4" t="s">
         <v>1065</v>
       </c>
@@ -20576,7 +20576,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="397" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:16">
       <c r="A397" s="4" t="s">
         <v>1067</v>
       </c>
@@ -20605,7 +20605,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="398" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:16">
       <c r="A398" s="4" t="s">
         <v>1069</v>
       </c>
@@ -20649,7 +20649,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="399" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:16">
       <c r="A399" s="4" t="s">
         <v>1071</v>
       </c>
@@ -20678,7 +20678,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="400" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:16">
       <c r="A400" s="4" t="s">
         <v>1073</v>
       </c>
@@ -20707,7 +20707,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:16">
       <c r="A401" s="4" t="s">
         <v>1075</v>
       </c>
@@ -20736,7 +20736,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="402" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:16">
       <c r="A402" s="4" t="s">
         <v>1077</v>
       </c>
@@ -20765,7 +20765,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="403" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:16">
       <c r="A403" s="4" t="s">
         <v>1079</v>
       </c>
@@ -20794,7 +20794,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="404" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:16">
       <c r="A404" s="4" t="s">
         <v>1081</v>
       </c>
@@ -20817,7 +20817,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:16">
       <c r="A405" s="4" t="s">
         <v>1083</v>
       </c>
@@ -20858,7 +20858,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="406" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:16">
       <c r="A406" s="4" t="s">
         <v>1089</v>
       </c>
@@ -20896,7 +20896,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="407" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:16">
       <c r="A407" s="4" t="s">
         <v>1091</v>
       </c>
@@ -20937,7 +20937,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="408" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:16">
       <c r="A408" s="4" t="s">
         <v>1093</v>
       </c>
@@ -20981,7 +20981,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="409" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:16">
       <c r="A409" s="4" t="s">
         <v>1095</v>
       </c>
@@ -21010,7 +21010,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:16">
       <c r="A410" s="4" t="s">
         <v>1097</v>
       </c>
@@ -21042,7 +21042,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="411" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:16">
       <c r="A411" s="4" t="s">
         <v>1099</v>
       </c>
@@ -21077,7 +21077,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="412" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:16">
       <c r="A412" s="4" t="s">
         <v>1103</v>
       </c>
@@ -21121,7 +21121,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="413" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:16">
       <c r="A413" s="4" t="s">
         <v>1105</v>
       </c>
@@ -21156,7 +21156,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:16">
       <c r="A414" s="4" t="s">
         <v>1107</v>
       </c>
@@ -21194,7 +21194,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:16">
       <c r="A415" s="4" t="s">
         <v>1109</v>
       </c>
@@ -21238,7 +21238,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="416" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:16">
       <c r="A416" s="4" t="s">
         <v>1111</v>
       </c>
@@ -21267,7 +21267,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="417" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:16">
       <c r="A417" s="4" t="s">
         <v>1113</v>
       </c>
@@ -21311,7 +21311,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="418" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:16">
       <c r="A418" s="4" t="s">
         <v>1117</v>
       </c>
@@ -21355,7 +21355,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="419" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:16">
       <c r="A419" s="4" t="s">
         <v>1119</v>
       </c>
@@ -21399,7 +21399,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="420" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:16">
       <c r="A420" s="4" t="s">
         <v>1121</v>
       </c>
@@ -21437,7 +21437,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:16">
       <c r="A421" s="4" t="s">
         <v>1123</v>
       </c>
@@ -21481,7 +21481,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="422" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:16">
       <c r="A422" s="4" t="s">
         <v>1125</v>
       </c>
@@ -21510,7 +21510,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="423" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:16">
       <c r="A423" s="4" t="s">
         <v>1127</v>
       </c>
@@ -21539,7 +21539,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="424" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:16">
       <c r="A424" s="4" t="s">
         <v>1129</v>
       </c>
@@ -21583,7 +21583,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="425" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:16">
       <c r="A425" s="4" t="s">
         <v>1131</v>
       </c>
@@ -21612,7 +21612,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="426" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:16">
       <c r="A426" s="4" t="s">
         <v>1133</v>
       </c>
@@ -21650,7 +21650,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="427" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:16">
       <c r="A427" s="4" t="s">
         <v>1136</v>
       </c>
@@ -21688,7 +21688,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="428" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:16">
       <c r="A428" s="4" t="s">
         <v>1138</v>
       </c>
@@ -21717,7 +21717,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="429" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:16">
       <c r="A429" s="4" t="s">
         <v>1142</v>
       </c>
@@ -21740,7 +21740,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="430" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:16">
       <c r="A430" s="4" t="s">
         <v>1144</v>
       </c>
@@ -21784,7 +21784,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="431" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:16">
       <c r="A431" s="4" t="s">
         <v>1148</v>
       </c>
@@ -21816,7 +21816,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="432" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:16">
       <c r="A432" s="4" t="s">
         <v>1150</v>
       </c>
@@ -21851,7 +21851,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="433" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:16">
       <c r="A433" s="4" t="s">
         <v>1152</v>
       </c>
@@ -21880,7 +21880,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="434" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:16">
       <c r="A434" s="4" t="s">
         <v>1154</v>
       </c>
@@ -21909,7 +21909,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="435" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:16">
       <c r="A435" s="4" t="s">
         <v>1156</v>
       </c>
@@ -21953,7 +21953,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="436" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:16">
       <c r="A436" s="4" t="s">
         <v>1158</v>
       </c>
@@ -21982,7 +21982,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="437" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:16">
       <c r="A437" s="4" t="s">
         <v>1160</v>
       </c>
@@ -22039,15 +22039,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7312EB9-07A9-6641-ACD7-57F691F1F395}">
   <dimension ref="A1:E427"/>
-  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="50.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.81640625" customWidth="1"/>
-    <col min="5" max="5" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -22064,7 +22064,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>111</v>
       </c>
@@ -22081,7 +22081,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>112</v>
       </c>
@@ -22098,7 +22098,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>113</v>
       </c>
@@ -22115,7 +22115,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>114</v>
       </c>
@@ -22132,7 +22132,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>115</v>
       </c>
@@ -22149,7 +22149,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>116</v>
       </c>
@@ -22166,7 +22166,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>119</v>
       </c>
@@ -22183,7 +22183,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>121</v>
       </c>
@@ -22200,7 +22200,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>122</v>
       </c>
@@ -22217,7 +22217,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>123</v>
       </c>
@@ -22234,7 +22234,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>124</v>
       </c>
@@ -22251,7 +22251,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>125</v>
       </c>
@@ -22268,7 +22268,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>126</v>
       </c>
@@ -22285,7 +22285,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>127</v>
       </c>
@@ -22302,7 +22302,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>128</v>
       </c>
@@ -22319,7 +22319,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>129</v>
       </c>
@@ -22336,7 +22336,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>130</v>
       </c>
@@ -22353,7 +22353,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>141</v>
       </c>
@@ -22370,7 +22370,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>142</v>
       </c>
@@ -22387,7 +22387,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>143</v>
       </c>
@@ -22404,7 +22404,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>144</v>
       </c>
@@ -22421,7 +22421,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>145</v>
       </c>
@@ -22438,7 +22438,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>146</v>
       </c>
@@ -22455,7 +22455,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>149</v>
       </c>
@@ -22472,7 +22472,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>150</v>
       </c>
@@ -22489,7 +22489,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>161</v>
       </c>
@@ -22506,7 +22506,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>162</v>
       </c>
@@ -22523,7 +22523,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>163</v>
       </c>
@@ -22540,7 +22540,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>164</v>
       </c>
@@ -22557,7 +22557,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>170</v>
       </c>
@@ -22574,7 +22574,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>210</v>
       </c>
@@ -22591,7 +22591,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>220</v>
       </c>
@@ -22608,7 +22608,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5">
       <c r="A34">
         <v>230</v>
       </c>
@@ -22625,7 +22625,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5">
       <c r="A35">
         <v>240</v>
       </c>
@@ -22642,7 +22642,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5">
       <c r="A36">
         <v>311</v>
       </c>
@@ -22659,7 +22659,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>312</v>
       </c>
@@ -22676,7 +22676,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5">
       <c r="A38">
         <v>321</v>
       </c>
@@ -22693,7 +22693,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5">
       <c r="A39">
         <v>322</v>
       </c>
@@ -22710,7 +22710,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5">
       <c r="A40">
         <v>9000</v>
       </c>
@@ -22727,7 +22727,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5">
       <c r="A41">
         <v>9101</v>
       </c>
@@ -22744,7 +22744,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5">
       <c r="A42">
         <v>9102</v>
       </c>
@@ -22761,7 +22761,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5">
       <c r="A43">
         <v>9103</v>
       </c>
@@ -22778,7 +22778,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5">
       <c r="A44">
         <v>9200</v>
       </c>
@@ -22795,7 +22795,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>9311</v>
       </c>
@@ -22812,7 +22812,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>9312</v>
       </c>
@@ -22829,7 +22829,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5">
       <c r="A47">
         <v>9319</v>
       </c>
@@ -22846,7 +22846,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5">
       <c r="A48">
         <v>9321</v>
       </c>
@@ -22863,7 +22863,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5">
       <c r="A49">
         <v>9329</v>
       </c>
@@ -22880,7 +22880,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5">
       <c r="A50">
         <v>9411</v>
       </c>
@@ -22897,7 +22897,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5">
       <c r="A51">
         <v>9412</v>
       </c>
@@ -22914,7 +22914,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5">
       <c r="A52">
         <v>9420</v>
       </c>
@@ -22931,7 +22931,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5">
       <c r="A53">
         <v>9491</v>
       </c>
@@ -22948,7 +22948,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5">
       <c r="A54">
         <v>9492</v>
       </c>
@@ -22965,7 +22965,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5">
       <c r="A55">
         <v>9499</v>
       </c>
@@ -22982,7 +22982,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5">
       <c r="A56">
         <v>9603</v>
       </c>
@@ -22999,7 +22999,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5">
       <c r="A57">
         <v>9609</v>
       </c>
@@ -23016,7 +23016,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5">
       <c r="A58">
         <v>9700</v>
       </c>
@@ -23033,7 +23033,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5">
       <c r="A59">
         <v>9810</v>
       </c>
@@ -23050,7 +23050,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5">
       <c r="A60">
         <v>9820</v>
       </c>
@@ -23067,7 +23067,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5">
       <c r="A61">
         <v>4100</v>
       </c>
@@ -23084,7 +23084,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5">
       <c r="A62">
         <v>4210</v>
       </c>
@@ -23101,7 +23101,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5">
       <c r="A63">
         <v>4220</v>
       </c>
@@ -23118,7 +23118,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5">
       <c r="A64">
         <v>4290</v>
       </c>
@@ -23135,7 +23135,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5">
       <c r="A65">
         <v>4311</v>
       </c>
@@ -23152,7 +23152,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5">
       <c r="A66">
         <v>4312</v>
       </c>
@@ -23169,7 +23169,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5">
       <c r="A67">
         <v>4321</v>
       </c>
@@ -23186,7 +23186,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5">
       <c r="A68">
         <v>4322</v>
       </c>
@@ -23203,7 +23203,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5">
       <c r="A69">
         <v>4329</v>
       </c>
@@ -23220,7 +23220,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5">
       <c r="A70">
         <v>4330</v>
       </c>
@@ -23237,7 +23237,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5">
       <c r="A71">
         <v>4390</v>
       </c>
@@ -23254,7 +23254,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5">
       <c r="A72">
         <v>202</v>
       </c>
@@ -23271,7 +23271,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5">
       <c r="A73">
         <v>1010</v>
       </c>
@@ -23288,7 +23288,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5">
       <c r="A74">
         <v>1020</v>
       </c>
@@ -23305,7 +23305,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5">
       <c r="A75">
         <v>1030</v>
       </c>
@@ -23322,7 +23322,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5">
       <c r="A76">
         <v>1040</v>
       </c>
@@ -23339,7 +23339,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5">
       <c r="A77">
         <v>1050</v>
       </c>
@@ -23356,7 +23356,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5">
       <c r="A78">
         <v>1061</v>
       </c>
@@ -23373,7 +23373,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5">
       <c r="A79">
         <v>1062</v>
       </c>
@@ -23390,7 +23390,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5">
       <c r="A80">
         <v>1071</v>
       </c>
@@ -23407,7 +23407,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5">
       <c r="A81">
         <v>1072</v>
       </c>
@@ -23424,7 +23424,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5">
       <c r="A82">
         <v>1073</v>
       </c>
@@ -23441,7 +23441,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5">
       <c r="A83">
         <v>1074</v>
       </c>
@@ -23458,7 +23458,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5">
       <c r="A84">
         <v>1075</v>
       </c>
@@ -23475,7 +23475,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5">
       <c r="A85">
         <v>1079</v>
       </c>
@@ -23492,7 +23492,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5">
       <c r="A86">
         <v>1080</v>
       </c>
@@ -23509,7 +23509,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5">
       <c r="A87">
         <v>1101</v>
       </c>
@@ -23526,7 +23526,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5">
       <c r="A88">
         <v>1102</v>
       </c>
@@ -23543,7 +23543,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5">
       <c r="A89">
         <v>1103</v>
       </c>
@@ -23560,7 +23560,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5">
       <c r="A90">
         <v>1104</v>
       </c>
@@ -23577,7 +23577,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5">
       <c r="A91">
         <v>1200</v>
       </c>
@@ -23594,7 +23594,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5">
       <c r="A92">
         <v>1311</v>
       </c>
@@ -23611,7 +23611,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5">
       <c r="A93">
         <v>1312</v>
       </c>
@@ -23628,7 +23628,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5">
       <c r="A94">
         <v>1313</v>
       </c>
@@ -23645,7 +23645,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5">
       <c r="A95">
         <v>1391</v>
       </c>
@@ -23662,7 +23662,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5">
       <c r="A96">
         <v>1392</v>
       </c>
@@ -23679,7 +23679,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5">
       <c r="A97">
         <v>1393</v>
       </c>
@@ -23696,7 +23696,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5">
       <c r="A98">
         <v>1394</v>
       </c>
@@ -23713,7 +23713,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5">
       <c r="A99">
         <v>1399</v>
       </c>
@@ -23730,7 +23730,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5">
       <c r="A100">
         <v>1410</v>
       </c>
@@ -23747,7 +23747,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5">
       <c r="A101">
         <v>1420</v>
       </c>
@@ -23764,7 +23764,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5">
       <c r="A102">
         <v>1430</v>
       </c>
@@ -23781,7 +23781,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5">
       <c r="A103">
         <v>1511</v>
       </c>
@@ -23798,7 +23798,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5">
       <c r="A104">
         <v>1512</v>
       </c>
@@ -23815,7 +23815,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5">
       <c r="A105">
         <v>1520</v>
       </c>
@@ -23832,7 +23832,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5">
       <c r="A106">
         <v>1610</v>
       </c>
@@ -23849,7 +23849,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5">
       <c r="A107">
         <v>1621</v>
       </c>
@@ -23866,7 +23866,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5">
       <c r="A108">
         <v>1622</v>
       </c>
@@ -23883,7 +23883,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5">
       <c r="A109">
         <v>1623</v>
       </c>
@@ -23900,7 +23900,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:5">
       <c r="A110">
         <v>1629</v>
       </c>
@@ -23917,7 +23917,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5">
       <c r="A111">
         <v>1701</v>
       </c>
@@ -23934,7 +23934,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:5">
       <c r="A112">
         <v>1702</v>
       </c>
@@ -23951,7 +23951,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:5">
       <c r="A113">
         <v>1709</v>
       </c>
@@ -23968,7 +23968,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5">
       <c r="A114">
         <v>1811</v>
       </c>
@@ -23985,7 +23985,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:5">
       <c r="A115">
         <v>1812</v>
       </c>
@@ -24002,7 +24002,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:5">
       <c r="A116">
         <v>1820</v>
       </c>
@@ -24019,7 +24019,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:5">
       <c r="A117">
         <v>1910</v>
       </c>
@@ -24036,7 +24036,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:5">
       <c r="A118">
         <v>1920</v>
       </c>
@@ -24053,7 +24053,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:5">
       <c r="A119">
         <v>2011</v>
       </c>
@@ -24070,7 +24070,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5">
       <c r="A120">
         <v>2012</v>
       </c>
@@ -24087,7 +24087,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5">
       <c r="A121">
         <v>2013</v>
       </c>
@@ -24104,7 +24104,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:5">
       <c r="A122">
         <v>2021</v>
       </c>
@@ -24121,7 +24121,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:5">
       <c r="A123">
         <v>2022</v>
       </c>
@@ -24138,7 +24138,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:5">
       <c r="A124">
         <v>2023</v>
       </c>
@@ -24155,7 +24155,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:5">
       <c r="A125">
         <v>2029</v>
       </c>
@@ -24172,7 +24172,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:5">
       <c r="A126">
         <v>2030</v>
       </c>
@@ -24189,7 +24189,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5">
       <c r="A127">
         <v>2100</v>
       </c>
@@ -24206,7 +24206,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:5">
       <c r="A128">
         <v>2211</v>
       </c>
@@ -24223,7 +24223,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:5">
       <c r="A129">
         <v>2219</v>
       </c>
@@ -24240,7 +24240,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5">
       <c r="A130">
         <v>2220</v>
       </c>
@@ -24257,7 +24257,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:5">
       <c r="A131">
         <v>2310</v>
       </c>
@@ -24274,7 +24274,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:5">
       <c r="A132">
         <v>2391</v>
       </c>
@@ -24291,7 +24291,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:5">
       <c r="A133">
         <v>2392</v>
       </c>
@@ -24308,7 +24308,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:5">
       <c r="A134">
         <v>2393</v>
       </c>
@@ -24325,7 +24325,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:5">
       <c r="A135">
         <v>2394</v>
       </c>
@@ -24342,7 +24342,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:5">
       <c r="A136">
         <v>2395</v>
       </c>
@@ -24359,7 +24359,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5">
       <c r="A137">
         <v>2396</v>
       </c>
@@ -24376,7 +24376,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:5">
       <c r="A138">
         <v>2399</v>
       </c>
@@ -24393,7 +24393,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:5">
       <c r="A139">
         <v>2410</v>
       </c>
@@ -24410,7 +24410,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:5">
       <c r="A140">
         <v>2420</v>
       </c>
@@ -24427,7 +24427,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5">
       <c r="A141">
         <v>2431</v>
       </c>
@@ -24444,7 +24444,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:5">
       <c r="A142">
         <v>2432</v>
       </c>
@@ -24461,7 +24461,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:5">
       <c r="A143">
         <v>2511</v>
       </c>
@@ -24478,7 +24478,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:5">
       <c r="A144">
         <v>2512</v>
       </c>
@@ -24495,7 +24495,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5">
       <c r="A145">
         <v>2513</v>
       </c>
@@ -24512,7 +24512,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:5">
       <c r="A146">
         <v>2520</v>
       </c>
@@ -24529,7 +24529,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:5">
       <c r="A147">
         <v>2591</v>
       </c>
@@ -24546,7 +24546,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:5">
       <c r="A148">
         <v>2592</v>
       </c>
@@ -24563,7 +24563,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:5">
       <c r="A149">
         <v>2593</v>
       </c>
@@ -24580,7 +24580,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5">
       <c r="A150">
         <v>2599</v>
       </c>
@@ -24597,7 +24597,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5">
       <c r="A151">
         <v>2610</v>
       </c>
@@ -24614,7 +24614,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:5">
       <c r="A152">
         <v>2620</v>
       </c>
@@ -24631,7 +24631,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:5">
       <c r="A153">
         <v>2630</v>
       </c>
@@ -24648,7 +24648,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:5">
       <c r="A154">
         <v>2640</v>
       </c>
@@ -24665,7 +24665,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:5">
       <c r="A155">
         <v>2651</v>
       </c>
@@ -24682,7 +24682,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5">
       <c r="A156">
         <v>2652</v>
       </c>
@@ -24699,7 +24699,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:5">
       <c r="A157">
         <v>2660</v>
       </c>
@@ -24716,7 +24716,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:5">
       <c r="A158">
         <v>2670</v>
       </c>
@@ -24733,7 +24733,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5">
       <c r="A159">
         <v>2680</v>
       </c>
@@ -24750,7 +24750,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:5">
       <c r="A160">
         <v>2710</v>
       </c>
@@ -24767,7 +24767,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:5">
       <c r="A161">
         <v>2720</v>
       </c>
@@ -24784,7 +24784,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5">
       <c r="A162">
         <v>2731</v>
       </c>
@@ -24801,7 +24801,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5">
       <c r="A163">
         <v>2732</v>
       </c>
@@ -24818,7 +24818,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5">
       <c r="A164">
         <v>2733</v>
       </c>
@@ -24835,7 +24835,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5">
       <c r="A165">
         <v>2740</v>
       </c>
@@ -24852,7 +24852,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:5">
       <c r="A166">
         <v>2750</v>
       </c>
@@ -24869,7 +24869,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:5">
       <c r="A167">
         <v>2790</v>
       </c>
@@ -24886,7 +24886,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:5">
       <c r="A168">
         <v>2811</v>
       </c>
@@ -24903,7 +24903,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:5">
       <c r="A169">
         <v>2812</v>
       </c>
@@ -24920,7 +24920,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:5">
       <c r="A170">
         <v>2813</v>
       </c>
@@ -24937,7 +24937,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5">
       <c r="A171">
         <v>2814</v>
       </c>
@@ -24954,7 +24954,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:5">
       <c r="A172">
         <v>2815</v>
       </c>
@@ -24971,7 +24971,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:5">
       <c r="A173">
         <v>2816</v>
       </c>
@@ -24988,7 +24988,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:5">
       <c r="A174">
         <v>2817</v>
       </c>
@@ -25005,7 +25005,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:5">
       <c r="A175">
         <v>2818</v>
       </c>
@@ -25022,7 +25022,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:5">
       <c r="A176">
         <v>2819</v>
       </c>
@@ -25039,7 +25039,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:5">
       <c r="A177">
         <v>2821</v>
       </c>
@@ -25056,7 +25056,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:5">
       <c r="A178">
         <v>2822</v>
       </c>
@@ -25073,7 +25073,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:5">
       <c r="A179">
         <v>2823</v>
       </c>
@@ -25090,7 +25090,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:5">
       <c r="A180">
         <v>2824</v>
       </c>
@@ -25107,7 +25107,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:5">
       <c r="A181">
         <v>2825</v>
       </c>
@@ -25124,7 +25124,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:5">
       <c r="A182">
         <v>2826</v>
       </c>
@@ -25141,7 +25141,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:5">
       <c r="A183">
         <v>2829</v>
       </c>
@@ -25158,7 +25158,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:5">
       <c r="A184">
         <v>2910</v>
       </c>
@@ -25175,7 +25175,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:5">
       <c r="A185">
         <v>2920</v>
       </c>
@@ -25192,7 +25192,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:5">
       <c r="A186">
         <v>2930</v>
       </c>
@@ -25209,7 +25209,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:5">
       <c r="A187">
         <v>3011</v>
       </c>
@@ -25226,7 +25226,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:5">
       <c r="A188">
         <v>3012</v>
       </c>
@@ -25243,7 +25243,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:5">
       <c r="A189">
         <v>3020</v>
       </c>
@@ -25260,7 +25260,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:5">
       <c r="A190">
         <v>3030</v>
       </c>
@@ -25277,7 +25277,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:5">
       <c r="A191">
         <v>3040</v>
       </c>
@@ -25294,7 +25294,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5">
       <c r="A192">
         <v>3091</v>
       </c>
@@ -25311,7 +25311,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:5">
       <c r="A193">
         <v>3092</v>
       </c>
@@ -25328,7 +25328,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:5">
       <c r="A194">
         <v>3099</v>
       </c>
@@ -25345,7 +25345,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:5">
       <c r="A195">
         <v>3100</v>
       </c>
@@ -25362,7 +25362,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:5">
       <c r="A196">
         <v>3211</v>
       </c>
@@ -25379,7 +25379,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:5">
       <c r="A197">
         <v>3212</v>
       </c>
@@ -25396,7 +25396,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:5">
       <c r="A198">
         <v>3220</v>
       </c>
@@ -25413,7 +25413,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:5">
       <c r="A199">
         <v>3230</v>
       </c>
@@ -25430,7 +25430,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:5">
       <c r="A200">
         <v>3240</v>
       </c>
@@ -25447,7 +25447,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:5">
       <c r="A201">
         <v>3250</v>
       </c>
@@ -25464,7 +25464,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:5">
       <c r="A202">
         <v>3290</v>
       </c>
@@ -25481,7 +25481,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:5">
       <c r="A203">
         <v>3311</v>
       </c>
@@ -25498,7 +25498,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:5">
       <c r="A204">
         <v>3312</v>
       </c>
@@ -25515,7 +25515,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:5">
       <c r="A205">
         <v>3313</v>
       </c>
@@ -25532,7 +25532,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:5">
       <c r="A206">
         <v>3314</v>
       </c>
@@ -25549,7 +25549,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:5">
       <c r="A207">
         <v>3315</v>
       </c>
@@ -25566,7 +25566,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:5">
       <c r="A208">
         <v>3319</v>
       </c>
@@ -25583,7 +25583,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:5">
       <c r="A209">
         <v>3320</v>
       </c>
@@ -25600,7 +25600,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:5">
       <c r="A210">
         <v>477</v>
       </c>
@@ -25617,7 +25617,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5">
       <c r="A211">
         <v>478</v>
       </c>
@@ -25634,7 +25634,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5">
       <c r="A212">
         <v>479</v>
       </c>
@@ -25651,7 +25651,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5">
       <c r="A213">
         <v>492</v>
       </c>
@@ -25668,7 +25668,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5">
       <c r="A214">
         <v>4510</v>
       </c>
@@ -25685,7 +25685,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5">
       <c r="A215">
         <v>4520</v>
       </c>
@@ -25702,7 +25702,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5">
       <c r="A216">
         <v>4530</v>
       </c>
@@ -25719,7 +25719,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5">
       <c r="A217">
         <v>4540</v>
       </c>
@@ -25736,7 +25736,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5">
       <c r="A218">
         <v>4610</v>
       </c>
@@ -25753,7 +25753,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5">
       <c r="A219">
         <v>4620</v>
       </c>
@@ -25770,7 +25770,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5">
       <c r="A220">
         <v>4630</v>
       </c>
@@ -25787,7 +25787,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5">
       <c r="A221">
         <v>4641</v>
       </c>
@@ -25804,7 +25804,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5">
       <c r="A222">
         <v>4649</v>
       </c>
@@ -25821,7 +25821,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5">
       <c r="A223">
         <v>4651</v>
       </c>
@@ -25838,7 +25838,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5">
       <c r="A224">
         <v>4652</v>
       </c>
@@ -25855,7 +25855,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5">
       <c r="A225">
         <v>4653</v>
       </c>
@@ -25872,7 +25872,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5">
       <c r="A226">
         <v>4659</v>
       </c>
@@ -25889,7 +25889,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5">
       <c r="A227">
         <v>4661</v>
       </c>
@@ -25906,7 +25906,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5">
       <c r="A228">
         <v>4662</v>
       </c>
@@ -25923,7 +25923,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5">
       <c r="A229">
         <v>4663</v>
       </c>
@@ -25940,7 +25940,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:5">
       <c r="A230">
         <v>4669</v>
       </c>
@@ -25957,7 +25957,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5">
       <c r="A231">
         <v>4690</v>
       </c>
@@ -25974,7 +25974,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5">
       <c r="A232">
         <v>4711</v>
       </c>
@@ -25991,7 +25991,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:5">
       <c r="A233">
         <v>4719</v>
       </c>
@@ -26008,7 +26008,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5">
       <c r="A234">
         <v>4721</v>
       </c>
@@ -26025,7 +26025,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5">
       <c r="A235">
         <v>4722</v>
       </c>
@@ -26042,7 +26042,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5">
       <c r="A236">
         <v>4723</v>
       </c>
@@ -26059,7 +26059,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5">
       <c r="A237">
         <v>4730</v>
       </c>
@@ -26076,7 +26076,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5">
       <c r="A238">
         <v>4741</v>
       </c>
@@ -26093,7 +26093,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5">
       <c r="A239">
         <v>4742</v>
       </c>
@@ -26110,7 +26110,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5">
       <c r="A240">
         <v>4751</v>
       </c>
@@ -26127,7 +26127,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:5">
       <c r="A241">
         <v>4752</v>
       </c>
@@ -26144,7 +26144,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:5">
       <c r="A242">
         <v>4753</v>
       </c>
@@ -26161,7 +26161,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:5">
       <c r="A243">
         <v>4759</v>
       </c>
@@ -26178,7 +26178,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:5">
       <c r="A244">
         <v>4761</v>
       </c>
@@ -26195,7 +26195,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:5">
       <c r="A245">
         <v>4762</v>
       </c>
@@ -26212,7 +26212,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:5">
       <c r="A246">
         <v>4763</v>
       </c>
@@ -26229,7 +26229,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:5">
       <c r="A247">
         <v>4764</v>
       </c>
@@ -26246,7 +26246,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:5">
       <c r="A248">
         <v>4771</v>
       </c>
@@ -26263,7 +26263,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:5">
       <c r="A249">
         <v>4772</v>
       </c>
@@ -26280,7 +26280,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:5">
       <c r="A250">
         <v>4773</v>
       </c>
@@ -26297,7 +26297,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:5">
       <c r="A251">
         <v>4774</v>
       </c>
@@ -26314,7 +26314,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:5">
       <c r="A252">
         <v>4781</v>
       </c>
@@ -26331,7 +26331,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:5">
       <c r="A253">
         <v>4782</v>
       </c>
@@ -26348,7 +26348,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:5">
       <c r="A254">
         <v>4789</v>
       </c>
@@ -26365,7 +26365,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:5">
       <c r="A255">
         <v>4791</v>
       </c>
@@ -26382,7 +26382,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:5">
       <c r="A256">
         <v>4799</v>
       </c>
@@ -26399,7 +26399,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:5">
       <c r="A257">
         <v>4911</v>
       </c>
@@ -26416,7 +26416,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:5">
       <c r="A258">
         <v>4912</v>
       </c>
@@ -26433,7 +26433,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:5">
       <c r="A259">
         <v>4921</v>
       </c>
@@ -26450,7 +26450,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:5">
       <c r="A260">
         <v>4922</v>
       </c>
@@ -26467,7 +26467,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:5">
       <c r="A261">
         <v>4923</v>
       </c>
@@ -26484,7 +26484,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:5">
       <c r="A262">
         <v>4930</v>
       </c>
@@ -26501,7 +26501,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:5">
       <c r="A263">
         <v>5011</v>
       </c>
@@ -26518,7 +26518,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:5">
       <c r="A264">
         <v>5012</v>
       </c>
@@ -26535,7 +26535,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:5">
       <c r="A265">
         <v>5021</v>
       </c>
@@ -26552,7 +26552,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:5">
       <c r="A266">
         <v>5022</v>
       </c>
@@ -26569,7 +26569,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:5">
       <c r="A267">
         <v>5110</v>
       </c>
@@ -26586,7 +26586,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:5">
       <c r="A268">
         <v>5120</v>
       </c>
@@ -26603,7 +26603,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:5">
       <c r="A269">
         <v>5210</v>
       </c>
@@ -26620,7 +26620,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:5">
       <c r="A270">
         <v>5221</v>
       </c>
@@ -26637,7 +26637,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:5">
       <c r="A271">
         <v>5222</v>
       </c>
@@ -26654,7 +26654,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:5">
       <c r="A272">
         <v>5223</v>
       </c>
@@ -26671,7 +26671,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:5">
       <c r="A273">
         <v>5224</v>
       </c>
@@ -26688,7 +26688,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:5">
       <c r="A274">
         <v>5229</v>
       </c>
@@ -26705,7 +26705,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:5">
       <c r="A275">
         <v>5310</v>
       </c>
@@ -26722,7 +26722,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:5">
       <c r="A276">
         <v>5320</v>
       </c>
@@ -26739,7 +26739,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:5">
       <c r="A277">
         <v>5510</v>
       </c>
@@ -26756,7 +26756,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:5">
       <c r="A278">
         <v>5520</v>
       </c>
@@ -26773,7 +26773,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:5">
       <c r="A279">
         <v>5590</v>
       </c>
@@ -26790,7 +26790,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:5">
       <c r="A280">
         <v>5610</v>
       </c>
@@ -26807,7 +26807,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:5">
       <c r="A281">
         <v>5621</v>
       </c>
@@ -26824,7 +26824,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:5">
       <c r="A282">
         <v>5629</v>
       </c>
@@ -26841,7 +26841,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:5">
       <c r="A283">
         <v>5630</v>
       </c>
@@ -26858,7 +26858,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:5">
       <c r="A284">
         <v>5811</v>
       </c>
@@ -26875,7 +26875,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:5">
       <c r="A285">
         <v>5812</v>
       </c>
@@ -26892,7 +26892,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:5">
       <c r="A286">
         <v>5813</v>
       </c>
@@ -26909,7 +26909,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:5">
       <c r="A287">
         <v>5819</v>
       </c>
@@ -26926,7 +26926,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:5">
       <c r="A288">
         <v>5820</v>
       </c>
@@ -26943,7 +26943,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:5">
       <c r="A289">
         <v>5911</v>
       </c>
@@ -26960,7 +26960,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:5">
       <c r="A290">
         <v>5912</v>
       </c>
@@ -26977,7 +26977,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:5">
       <c r="A291">
         <v>5913</v>
       </c>
@@ -26994,7 +26994,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:5">
       <c r="A292">
         <v>5914</v>
       </c>
@@ -27011,7 +27011,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:5">
       <c r="A293">
         <v>5920</v>
       </c>
@@ -27028,7 +27028,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:5">
       <c r="A294">
         <v>6010</v>
       </c>
@@ -27045,7 +27045,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:5">
       <c r="A295">
         <v>6020</v>
       </c>
@@ -27062,7 +27062,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:5">
       <c r="A296">
         <v>6110</v>
       </c>
@@ -27079,7 +27079,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:5">
       <c r="A297">
         <v>6120</v>
       </c>
@@ -27096,7 +27096,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:5">
       <c r="A298">
         <v>6130</v>
       </c>
@@ -27113,7 +27113,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:5">
       <c r="A299">
         <v>6190</v>
       </c>
@@ -27130,7 +27130,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:5">
       <c r="A300">
         <v>6201</v>
       </c>
@@ -27147,7 +27147,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:5">
       <c r="A301">
         <v>6202</v>
       </c>
@@ -27164,7 +27164,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:5">
       <c r="A302">
         <v>6209</v>
       </c>
@@ -27181,7 +27181,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:5">
       <c r="A303">
         <v>6311</v>
       </c>
@@ -27198,7 +27198,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:5">
       <c r="A304">
         <v>6312</v>
       </c>
@@ -27215,7 +27215,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:5">
       <c r="A305">
         <v>6391</v>
       </c>
@@ -27232,7 +27232,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:5">
       <c r="A306">
         <v>6399</v>
       </c>
@@ -27249,7 +27249,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:5">
       <c r="A307">
         <v>6411</v>
       </c>
@@ -27266,7 +27266,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:5">
       <c r="A308">
         <v>6419</v>
       </c>
@@ -27283,7 +27283,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:5">
       <c r="A309">
         <v>6420</v>
       </c>
@@ -27300,7 +27300,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:5">
       <c r="A310">
         <v>6430</v>
       </c>
@@ -27317,7 +27317,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:5">
       <c r="A311">
         <v>6491</v>
       </c>
@@ -27334,7 +27334,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:5">
       <c r="A312">
         <v>6492</v>
       </c>
@@ -27351,7 +27351,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:5">
       <c r="A313">
         <v>6499</v>
       </c>
@@ -27368,7 +27368,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:5">
       <c r="A314">
         <v>6511</v>
       </c>
@@ -27385,7 +27385,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:5">
       <c r="A315">
         <v>6512</v>
       </c>
@@ -27402,7 +27402,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:5">
       <c r="A316">
         <v>6520</v>
       </c>
@@ -27419,7 +27419,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:5">
       <c r="A317">
         <v>6530</v>
       </c>
@@ -27436,7 +27436,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:5">
       <c r="A318">
         <v>6611</v>
       </c>
@@ -27453,7 +27453,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:5">
       <c r="A319">
         <v>6612</v>
       </c>
@@ -27470,7 +27470,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:5">
       <c r="A320">
         <v>6619</v>
       </c>
@@ -27487,7 +27487,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:5">
       <c r="A321">
         <v>6621</v>
       </c>
@@ -27504,7 +27504,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:5">
       <c r="A322">
         <v>6622</v>
       </c>
@@ -27521,7 +27521,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:5">
       <c r="A323">
         <v>6629</v>
       </c>
@@ -27538,7 +27538,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:5">
       <c r="A324">
         <v>6630</v>
       </c>
@@ -27555,7 +27555,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:5">
       <c r="A325">
         <v>6810</v>
       </c>
@@ -27572,7 +27572,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:5">
       <c r="A326">
         <v>6820</v>
       </c>
@@ -27589,7 +27589,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:5">
       <c r="A327">
         <v>6910</v>
       </c>
@@ -27606,7 +27606,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:5">
       <c r="A328">
         <v>6920</v>
       </c>
@@ -27623,7 +27623,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:5">
       <c r="A329">
         <v>7010</v>
       </c>
@@ -27640,7 +27640,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:5">
       <c r="A330">
         <v>7020</v>
       </c>
@@ -27657,7 +27657,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:5">
       <c r="A331">
         <v>7110</v>
       </c>
@@ -27674,7 +27674,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:5">
       <c r="A332">
         <v>7120</v>
       </c>
@@ -27691,7 +27691,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:5">
       <c r="A333">
         <v>7210</v>
       </c>
@@ -27708,7 +27708,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:5">
       <c r="A334">
         <v>7220</v>
       </c>
@@ -27725,7 +27725,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:5">
       <c r="A335">
         <v>7310</v>
       </c>
@@ -27742,7 +27742,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:5">
       <c r="A336">
         <v>7320</v>
       </c>
@@ -27759,7 +27759,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:5">
       <c r="A337">
         <v>7410</v>
       </c>
@@ -27776,7 +27776,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:5">
       <c r="A338">
         <v>7420</v>
       </c>
@@ -27793,7 +27793,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:5">
       <c r="A339">
         <v>7490</v>
       </c>
@@ -27810,7 +27810,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:5">
       <c r="A340">
         <v>7500</v>
       </c>
@@ -27827,7 +27827,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:5">
       <c r="A341">
         <v>7710</v>
       </c>
@@ -27844,7 +27844,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:5">
       <c r="A342">
         <v>7721</v>
       </c>
@@ -27861,7 +27861,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:5">
       <c r="A343">
         <v>7722</v>
       </c>
@@ -27878,7 +27878,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:5">
       <c r="A344">
         <v>7729</v>
       </c>
@@ -27895,7 +27895,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:5">
       <c r="A345">
         <v>7730</v>
       </c>
@@ -27912,7 +27912,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:5">
       <c r="A346">
         <v>7740</v>
       </c>
@@ -27929,7 +27929,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:5">
       <c r="A347">
         <v>7810</v>
       </c>
@@ -27946,7 +27946,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:5">
       <c r="A348">
         <v>7820</v>
       </c>
@@ -27963,7 +27963,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:5">
       <c r="A349">
         <v>7830</v>
       </c>
@@ -27980,7 +27980,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:5">
       <c r="A350">
         <v>7911</v>
       </c>
@@ -27997,7 +27997,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:5">
       <c r="A351">
         <v>7912</v>
       </c>
@@ -28014,7 +28014,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:5">
       <c r="A352">
         <v>7990</v>
       </c>
@@ -28031,7 +28031,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:5">
       <c r="A353">
         <v>8010</v>
       </c>
@@ -28048,7 +28048,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:5">
       <c r="A354">
         <v>8020</v>
       </c>
@@ -28065,7 +28065,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:5">
       <c r="A355">
         <v>8030</v>
       </c>
@@ -28082,7 +28082,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:5">
       <c r="A356">
         <v>8110</v>
       </c>
@@ -28099,7 +28099,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:5">
       <c r="A357">
         <v>8121</v>
       </c>
@@ -28116,7 +28116,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:5">
       <c r="A358">
         <v>8129</v>
       </c>
@@ -28133,7 +28133,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:5">
       <c r="A359">
         <v>8130</v>
       </c>
@@ -28150,7 +28150,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:5">
       <c r="A360">
         <v>8211</v>
       </c>
@@ -28167,7 +28167,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:5">
       <c r="A361">
         <v>8219</v>
       </c>
@@ -28184,7 +28184,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:5">
       <c r="A362">
         <v>8220</v>
       </c>
@@ -28201,7 +28201,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:5">
       <c r="A363">
         <v>8230</v>
       </c>
@@ -28218,7 +28218,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:5">
       <c r="A364">
         <v>8291</v>
       </c>
@@ -28235,7 +28235,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:5">
       <c r="A365">
         <v>8292</v>
       </c>
@@ -28252,7 +28252,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:5">
       <c r="A366">
         <v>8299</v>
       </c>
@@ -28269,7 +28269,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:5">
       <c r="A367">
         <v>9511</v>
       </c>
@@ -28286,7 +28286,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:5">
       <c r="A368">
         <v>9512</v>
       </c>
@@ -28303,7 +28303,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:5">
       <c r="A369">
         <v>9521</v>
       </c>
@@ -28320,7 +28320,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:5">
       <c r="A370">
         <v>9522</v>
       </c>
@@ -28337,7 +28337,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:5">
       <c r="A371">
         <v>9523</v>
       </c>
@@ -28354,7 +28354,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:5">
       <c r="A372">
         <v>9524</v>
       </c>
@@ -28371,7 +28371,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:5">
       <c r="A373">
         <v>9529</v>
       </c>
@@ -28388,7 +28388,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:5">
       <c r="A374">
         <v>9601</v>
       </c>
@@ -28405,7 +28405,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:5">
       <c r="A375">
         <v>9602</v>
       </c>
@@ -28422,7 +28422,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:5">
       <c r="A376">
         <v>510</v>
       </c>
@@ -28439,7 +28439,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:5">
       <c r="A377">
         <v>520</v>
       </c>
@@ -28456,7 +28456,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:5">
       <c r="A378">
         <v>610</v>
       </c>
@@ -28473,7 +28473,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:5">
       <c r="A379">
         <v>620</v>
       </c>
@@ -28490,7 +28490,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:5">
       <c r="A380">
         <v>663</v>
       </c>
@@ -28507,7 +28507,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:5">
       <c r="A381">
         <v>710</v>
       </c>
@@ -28524,7 +28524,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:5">
       <c r="A382">
         <v>721</v>
       </c>
@@ -28541,7 +28541,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:5">
       <c r="A383">
         <v>729</v>
       </c>
@@ -28558,7 +28558,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:5">
       <c r="A384">
         <v>810</v>
       </c>
@@ -28575,7 +28575,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:5">
       <c r="A385">
         <v>891</v>
       </c>
@@ -28592,7 +28592,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:5">
       <c r="A386">
         <v>892</v>
       </c>
@@ -28609,7 +28609,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:5">
       <c r="A387">
         <v>893</v>
       </c>
@@ -28626,7 +28626,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:5">
       <c r="A388">
         <v>899</v>
       </c>
@@ -28643,7 +28643,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:5">
       <c r="A389">
         <v>910</v>
       </c>
@@ -28660,7 +28660,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:5">
       <c r="A390">
         <v>932</v>
       </c>
@@ -28677,7 +28677,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:5">
       <c r="A391">
         <v>990</v>
       </c>
@@ -28694,7 +28694,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:5">
       <c r="A392">
         <v>3510</v>
       </c>
@@ -28711,7 +28711,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:5">
       <c r="A393">
         <v>3520</v>
       </c>
@@ -28728,7 +28728,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:5">
       <c r="A394">
         <v>3530</v>
       </c>
@@ -28745,7 +28745,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:5">
       <c r="A395">
         <v>3600</v>
       </c>
@@ -28762,7 +28762,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:5">
       <c r="A396">
         <v>3700</v>
       </c>
@@ -28779,7 +28779,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:5">
       <c r="A397">
         <v>3811</v>
       </c>
@@ -28796,7 +28796,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:5">
       <c r="A398">
         <v>3812</v>
       </c>
@@ -28813,7 +28813,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:5">
       <c r="A399">
         <v>3821</v>
       </c>
@@ -28830,7 +28830,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:5">
       <c r="A400">
         <v>3822</v>
       </c>
@@ -28847,7 +28847,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:5">
       <c r="A401">
         <v>3830</v>
       </c>
@@ -28864,7 +28864,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:5">
       <c r="A402">
         <v>3900</v>
       </c>
@@ -28881,7 +28881,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:5">
       <c r="A403">
         <v>8411</v>
       </c>
@@ -28898,7 +28898,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:5">
       <c r="A404">
         <v>8412</v>
       </c>
@@ -28915,7 +28915,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:5">
       <c r="A405">
         <v>8413</v>
       </c>
@@ -28932,7 +28932,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:5">
       <c r="A406">
         <v>8421</v>
       </c>
@@ -28949,7 +28949,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:5">
       <c r="A407">
         <v>8422</v>
       </c>
@@ -28966,7 +28966,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:5">
       <c r="A408">
         <v>8423</v>
       </c>
@@ -28983,7 +28983,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:5">
       <c r="A409">
         <v>8430</v>
       </c>
@@ -29000,7 +29000,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:5">
       <c r="A410">
         <v>8510</v>
       </c>
@@ -29017,7 +29017,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:5">
       <c r="A411">
         <v>8521</v>
       </c>
@@ -29034,7 +29034,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:5">
       <c r="A412">
         <v>8522</v>
       </c>
@@ -29051,7 +29051,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:5">
       <c r="A413">
         <v>8530</v>
       </c>
@@ -29068,7 +29068,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:5">
       <c r="A414">
         <v>8541</v>
       </c>
@@ -29085,7 +29085,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:5">
       <c r="A415">
         <v>8542</v>
       </c>
@@ -29102,7 +29102,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:5">
       <c r="A416">
         <v>8549</v>
       </c>
@@ -29119,7 +29119,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:5">
       <c r="A417">
         <v>8550</v>
       </c>
@@ -29136,7 +29136,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:5">
       <c r="A418">
         <v>8610</v>
       </c>
@@ -29153,7 +29153,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:5">
       <c r="A419">
         <v>8620</v>
       </c>
@@ -29170,7 +29170,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:5">
       <c r="A420">
         <v>8690</v>
       </c>
@@ -29187,7 +29187,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:5">
       <c r="A421">
         <v>8710</v>
       </c>
@@ -29204,7 +29204,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:5">
       <c r="A422">
         <v>8720</v>
       </c>
@@ -29221,7 +29221,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:5">
       <c r="A423">
         <v>8730</v>
       </c>
@@ -29238,7 +29238,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:5">
       <c r="A424">
         <v>8790</v>
       </c>
@@ -29255,7 +29255,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:5">
       <c r="A425">
         <v>8810</v>
       </c>
@@ -29272,7 +29272,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:5">
       <c r="A426">
         <v>8890</v>
       </c>
@@ -29289,7 +29289,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:5">
       <c r="A427">
         <v>9900</v>
       </c>
@@ -29307,7 +29307,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C427">
+  <sortState ref="A2:C427">
     <sortCondition ref="C23"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -29318,14 +29318,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2DEA81F-4F9F-7543-8D03-FF11F2C25C4A}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="44.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -29339,7 +29339,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4">
       <c r="A2" s="6">
         <v>5419</v>
       </c>
@@ -29353,7 +29353,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4">
       <c r="A3" s="6">
         <v>9111</v>
       </c>
@@ -29367,7 +29367,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4">
       <c r="A4" s="6">
         <v>5311</v>
       </c>
@@ -29381,7 +29381,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4">
       <c r="A5" s="6">
         <v>6121</v>
       </c>
@@ -29395,7 +29395,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4">
       <c r="A6" s="6">
         <v>9313</v>
       </c>
@@ -29409,7 +29409,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4">
       <c r="A7" s="6">
         <v>5120</v>
       </c>
@@ -29423,7 +29423,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4">
       <c r="A8" s="6">
         <v>9211</v>
       </c>
@@ -29437,7 +29437,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4">
       <c r="A9" s="6">
         <v>9412</v>
       </c>
@@ -29451,7 +29451,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4">
       <c r="A10" s="6">
         <v>5153</v>
       </c>
@@ -29465,7 +29465,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4">
       <c r="A11" s="6">
         <v>9121</v>
       </c>
@@ -29479,7 +29479,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4">
       <c r="A12" s="6">
         <v>9112</v>
       </c>
@@ -29493,7 +29493,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4">
       <c r="A13" s="6">
         <v>9212</v>
       </c>
@@ -29507,7 +29507,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4">
       <c r="A14" s="6">
         <v>7114</v>
       </c>
@@ -29521,7 +29521,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4">
       <c r="A15" s="6">
         <v>5322</v>
       </c>
@@ -29535,7 +29535,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4">
       <c r="A16" s="6">
         <v>7413</v>
       </c>
@@ -29549,7 +29549,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4">
       <c r="A17" s="6">
         <v>7115</v>
       </c>
@@ -29563,7 +29563,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4">
       <c r="A18" s="6">
         <v>9129</v>
       </c>
@@ -29577,7 +29577,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4">
       <c r="A19" s="6">
         <v>7131</v>
       </c>
@@ -29591,7 +29591,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4">
       <c r="A20" s="6">
         <v>5161</v>
       </c>
@@ -29605,7 +29605,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4">
       <c r="A21" s="6">
         <v>9329</v>
       </c>
@@ -29619,7 +29619,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4">
       <c r="A22" s="6">
         <v>9213</v>
       </c>
@@ -29633,7 +29633,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4">
       <c r="A23" s="6">
         <v>9333</v>
       </c>
@@ -29647,7 +29647,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4">
       <c r="A24" s="6">
         <v>9624</v>
       </c>
@@ -29661,7 +29661,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4">
       <c r="A25" s="6">
         <v>7111</v>
       </c>
@@ -29675,7 +29675,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4">
       <c r="A26" s="6">
         <v>9312</v>
       </c>

--- a/Data/Excel/NLFS_III/Sanjeet_classification.xlsx
+++ b/Data/Excel/NLFS_III/Sanjeet_classification.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandeepsharma/Desktop/Research/Data Analysis/Formal Informal wage/Formal_Informal_wage/Data/Excel/NLFS_III/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandeepsharma/Desktop/Research/Data Analysis/Formal Informal wage/Formal_informal_wage/Data/Excel/NLFS_III/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{74E8EA6C-B9E8-744E-9975-27A5F7FCA523}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{2965F4EF-E90F-3147-A787-E8FDC7BBE19D}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="27320" windowHeight="14860" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27320" windowHeight="14860" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="education_III" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="jobs_III" sheetId="3" r:id="rId3"/>
     <sheet name="nsic" sheetId="4" r:id="rId4"/>
     <sheet name="nsic_III" sheetId="8" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6319" uniqueCount="1624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6362" uniqueCount="1624">
   <si>
     <t>value</t>
   </si>
@@ -29692,4 +29693,232 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65FEC614-E16B-5341-A69B-E09BA90C1C4A}">
+  <dimension ref="A1:A43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="59" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>